--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_telecom_wireless.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1752919773989625</v>
+        <v>0.174905476653205</v>
       </c>
       <c r="C2">
-        <v>938.0641998973031</v>
+        <v>932.5269238178752</v>
       </c>
       <c r="D2">
-        <v>802.264199897303</v>
+        <v>804.6659238178751</v>
       </c>
       <c r="E2">
-        <v>-426.4</v>
+        <v>-418.461</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.939000000000001</v>
       </c>
       <c r="G2">
         <v>135.8</v>
@@ -1451,28 +1451,28 @@
         <v>111</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3993317</v>
       </c>
       <c r="N2">
-        <v>111</v>
+        <v>110.6006683</v>
       </c>
       <c r="O2">
-        <v>26.64</v>
+        <v>26.54416039199999</v>
       </c>
       <c r="P2">
-        <v>84.35999999999999</v>
+        <v>84.05650790799999</v>
       </c>
       <c r="Q2">
-        <v>196.86</v>
+        <v>196.556507908</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1752919773989625</v>
+        <v>0.1762860572254596</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6411265641243018</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>277.9644090363975</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.174905476653205</v>
+        <v>0.1745189759074475</v>
       </c>
       <c r="C3">
-        <v>932.5269238178752</v>
+        <v>927.0040709123399</v>
       </c>
       <c r="D3">
-        <v>804.6659238178751</v>
+        <v>807.08207091234</v>
       </c>
       <c r="E3">
-        <v>-418.461</v>
+        <v>-410.522</v>
       </c>
       <c r="F3">
-        <v>7.939000000000001</v>
+        <v>15.878</v>
       </c>
       <c r="G3">
         <v>135.8</v>
@@ -1533,28 +1533,28 @@
         <v>111</v>
       </c>
       <c r="M3">
-        <v>0.3993317</v>
+        <v>0.7986634</v>
       </c>
       <c r="N3">
-        <v>110.6006683</v>
+        <v>110.2013366</v>
       </c>
       <c r="O3">
-        <v>26.54416039199999</v>
+        <v>26.448320784</v>
       </c>
       <c r="P3">
-        <v>84.05650790799999</v>
+        <v>83.75301581599999</v>
       </c>
       <c r="Q3">
-        <v>196.556507908</v>
+        <v>196.253015816</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1762860572254596</v>
+        <v>0.1773004243953546</v>
       </c>
       <c r="T3">
-        <v>0.6411265641243018</v>
+        <v>0.6461105275624152</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>277.9644090363975</v>
+        <v>138.9822045181988</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1745189759074475</v>
+        <v>0.17413247516169</v>
       </c>
       <c r="C4">
-        <v>927.0040709123399</v>
+        <v>921.4957714961331</v>
       </c>
       <c r="D4">
-        <v>807.08207091234</v>
+        <v>809.512771496133</v>
       </c>
       <c r="E4">
-        <v>-410.522</v>
+        <v>-402.583</v>
       </c>
       <c r="F4">
-        <v>15.878</v>
+        <v>23.817</v>
       </c>
       <c r="G4">
         <v>135.8</v>
@@ -1615,28 +1615,28 @@
         <v>111</v>
       </c>
       <c r="M4">
-        <v>0.7986634</v>
+        <v>1.1979951</v>
       </c>
       <c r="N4">
-        <v>110.2013366</v>
+        <v>109.8020049</v>
       </c>
       <c r="O4">
-        <v>26.448320784</v>
+        <v>26.35248117599999</v>
       </c>
       <c r="P4">
-        <v>83.75301581599999</v>
+        <v>83.44952372399999</v>
       </c>
       <c r="Q4">
-        <v>196.253015816</v>
+        <v>195.949523724</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1773004243953546</v>
+        <v>0.1783357063522578</v>
       </c>
       <c r="T4">
-        <v>0.6461105275624152</v>
+        <v>0.6511972531332733</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>138.9822045181988</v>
+        <v>92.6548030121325</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.17413247516169</v>
+        <v>0.1737459744159325</v>
       </c>
       <c r="C5">
-        <v>921.4957714961331</v>
+        <v>916.0021574593239</v>
       </c>
       <c r="D5">
-        <v>809.512771496133</v>
+        <v>811.9581574593238</v>
       </c>
       <c r="E5">
-        <v>-402.583</v>
+        <v>-394.644</v>
       </c>
       <c r="F5">
-        <v>23.817</v>
+        <v>31.756</v>
       </c>
       <c r="G5">
         <v>135.8</v>
@@ -1697,28 +1697,28 @@
         <v>111</v>
       </c>
       <c r="M5">
-        <v>1.1979951</v>
+        <v>1.5973268</v>
       </c>
       <c r="N5">
-        <v>109.8020049</v>
+        <v>109.4026732</v>
       </c>
       <c r="O5">
-        <v>26.35248117599999</v>
+        <v>26.256641568</v>
       </c>
       <c r="P5">
-        <v>83.44952372399999</v>
+        <v>83.14603163199999</v>
       </c>
       <c r="Q5">
-        <v>195.949523724</v>
+        <v>195.646031632</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1783357063522578</v>
+        <v>0.179392556683263</v>
       </c>
       <c r="T5">
-        <v>0.6511972531332733</v>
+        <v>0.6563899521535241</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>92.6548030121325</v>
+        <v>69.49110225909938</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1737459744159325</v>
+        <v>0.173359473670175</v>
       </c>
       <c r="C6">
-        <v>916.0021574593239</v>
+        <v>910.5233622904706</v>
       </c>
       <c r="D6">
-        <v>811.9581574593238</v>
+        <v>814.4183622904707</v>
       </c>
       <c r="E6">
-        <v>-394.644</v>
+        <v>-386.705</v>
       </c>
       <c r="F6">
-        <v>31.756</v>
+        <v>39.69500000000001</v>
       </c>
       <c r="G6">
         <v>135.8</v>
@@ -1779,28 +1779,28 @@
         <v>111</v>
       </c>
       <c r="M6">
-        <v>1.5973268</v>
+        <v>1.9966585</v>
       </c>
       <c r="N6">
-        <v>109.4026732</v>
+        <v>109.0033415</v>
       </c>
       <c r="O6">
-        <v>26.256641568</v>
+        <v>26.16080196</v>
       </c>
       <c r="P6">
-        <v>83.14603163199999</v>
+        <v>82.84253953999999</v>
       </c>
       <c r="Q6">
-        <v>195.646031632</v>
+        <v>195.34253954</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.179392556683263</v>
+        <v>0.1804716564949211</v>
       </c>
       <c r="T6">
-        <v>0.6563899521535241</v>
+        <v>0.6616919711531487</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>69.49110225909938</v>
+        <v>55.5928818072795</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.173359473670175</v>
+        <v>0.1729729729244175</v>
       </c>
       <c r="C7">
-        <v>910.5233622904706</v>
+        <v>905.059521100912</v>
       </c>
       <c r="D7">
-        <v>814.4183622904707</v>
+        <v>816.893521100912</v>
       </c>
       <c r="E7">
-        <v>-386.705</v>
+        <v>-378.766</v>
       </c>
       <c r="F7">
-        <v>39.69500000000001</v>
+        <v>47.63400000000001</v>
       </c>
       <c r="G7">
         <v>135.8</v>
@@ -1861,28 +1861,28 @@
         <v>111</v>
       </c>
       <c r="M7">
-        <v>1.9966585</v>
+        <v>2.3959902</v>
       </c>
       <c r="N7">
-        <v>109.0033415</v>
+        <v>108.6040098</v>
       </c>
       <c r="O7">
-        <v>26.16080196</v>
+        <v>26.06496235199999</v>
       </c>
       <c r="P7">
-        <v>82.84253953999999</v>
+        <v>82.53904744799999</v>
       </c>
       <c r="Q7">
-        <v>195.34253954</v>
+        <v>195.039047448</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1804716564949211</v>
+        <v>0.1815737158770399</v>
       </c>
       <c r="T7">
-        <v>0.6616919711531487</v>
+        <v>0.6671067990676589</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>55.5928818072795</v>
+        <v>46.32740150606624</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1729729729244175</v>
+        <v>0.17258647217866</v>
       </c>
       <c r="C8">
-        <v>905.059521100912</v>
+        <v>899.6107706495001</v>
       </c>
       <c r="D8">
-        <v>816.893521100912</v>
+        <v>819.3837706495001</v>
       </c>
       <c r="E8">
-        <v>-378.766</v>
+        <v>-370.8270000000001</v>
       </c>
       <c r="F8">
-        <v>47.634</v>
+        <v>55.573</v>
       </c>
       <c r="G8">
         <v>135.8</v>
@@ -1943,28 +1943,28 @@
         <v>111</v>
       </c>
       <c r="M8">
-        <v>2.3959902</v>
+        <v>2.7953219</v>
       </c>
       <c r="N8">
-        <v>108.6040098</v>
+        <v>108.2046781</v>
       </c>
       <c r="O8">
-        <v>26.06496235199999</v>
+        <v>25.96912274399999</v>
       </c>
       <c r="P8">
-        <v>82.53904744799999</v>
+        <v>82.23555535599999</v>
       </c>
       <c r="Q8">
-        <v>195.039047448</v>
+        <v>194.735555356</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1815737158770399</v>
+        <v>0.1826994754609247</v>
       </c>
       <c r="T8">
-        <v>0.6671067990676589</v>
+        <v>0.672638074894309</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>46.32740150606625</v>
+        <v>39.70920129091393</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.17258647217866</v>
+        <v>0.1721999714329025</v>
       </c>
       <c r="C9">
-        <v>899.6107706495001</v>
+        <v>894.1772493677901</v>
       </c>
       <c r="D9">
-        <v>819.3837706495001</v>
+        <v>821.8892493677902</v>
       </c>
       <c r="E9">
-        <v>-370.827</v>
+        <v>-362.888</v>
       </c>
       <c r="F9">
-        <v>55.57300000000001</v>
+        <v>63.51200000000001</v>
       </c>
       <c r="G9">
         <v>135.8</v>
@@ -2025,28 +2025,28 @@
         <v>111</v>
       </c>
       <c r="M9">
-        <v>2.795321900000001</v>
+        <v>3.1946536</v>
       </c>
       <c r="N9">
-        <v>108.2046781</v>
+        <v>107.8053464</v>
       </c>
       <c r="O9">
-        <v>25.96912274399999</v>
+        <v>25.873283136</v>
       </c>
       <c r="P9">
-        <v>82.23555535599999</v>
+        <v>81.93206326399999</v>
       </c>
       <c r="Q9">
-        <v>194.735555356</v>
+        <v>194.432063264</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1826994754609247</v>
+        <v>0.1838497080792418</v>
       </c>
       <c r="T9">
-        <v>0.672638074894309</v>
+        <v>0.6782895958476256</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>39.70920129091392</v>
+        <v>34.74555112954969</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1721999714329025</v>
+        <v>0.1718134706871449</v>
       </c>
       <c r="C10">
-        <v>894.1772493677901</v>
+        <v>888.7590973856929</v>
       </c>
       <c r="D10">
-        <v>821.8892493677902</v>
+        <v>824.4100973856929</v>
       </c>
       <c r="E10">
-        <v>-362.888</v>
+        <v>-354.949</v>
       </c>
       <c r="F10">
-        <v>63.51200000000001</v>
+        <v>71.45100000000001</v>
       </c>
       <c r="G10">
         <v>135.8</v>
@@ -2107,28 +2107,28 @@
         <v>111</v>
       </c>
       <c r="M10">
-        <v>3.1946536</v>
+        <v>3.5939853</v>
       </c>
       <c r="N10">
-        <v>107.8053464</v>
+        <v>107.4060147</v>
       </c>
       <c r="O10">
-        <v>25.873283136</v>
+        <v>25.777443528</v>
       </c>
       <c r="P10">
-        <v>81.93206326399999</v>
+        <v>81.62857117199999</v>
       </c>
       <c r="Q10">
-        <v>194.432063264</v>
+        <v>194.128571172</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1838497080792418</v>
+        <v>0.1850252205353241</v>
       </c>
       <c r="T10">
-        <v>0.6782895958476256</v>
+        <v>0.6840653260526633</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>34.74555112954969</v>
+        <v>30.8849343373775</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1718134706871449</v>
+        <v>0.1714269699413875</v>
       </c>
       <c r="C11">
-        <v>888.7590973856929</v>
+        <v>883.3564565575988</v>
       </c>
       <c r="D11">
-        <v>824.4100973856929</v>
+        <v>826.9464565575988</v>
       </c>
       <c r="E11">
-        <v>-354.949</v>
+        <v>-347.01</v>
       </c>
       <c r="F11">
-        <v>71.45100000000001</v>
+        <v>79.39</v>
       </c>
       <c r="G11">
         <v>135.8</v>
@@ -2189,28 +2189,28 @@
         <v>111</v>
       </c>
       <c r="M11">
-        <v>3.5939853</v>
+        <v>3.993317</v>
       </c>
       <c r="N11">
-        <v>107.4060147</v>
+        <v>107.006683</v>
       </c>
       <c r="O11">
-        <v>25.777443528</v>
+        <v>25.68160391999999</v>
       </c>
       <c r="P11">
-        <v>81.62857117199999</v>
+        <v>81.32507907999999</v>
       </c>
       <c r="Q11">
-        <v>194.128571172</v>
+        <v>193.82507908</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1850252205353241</v>
+        <v>0.1862268554904305</v>
       </c>
       <c r="T11">
-        <v>0.6840653260526633</v>
+        <v>0.6899694058178132</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.8849343373775</v>
+        <v>27.79644090363975</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1714269699413875</v>
+        <v>0.17104046919563</v>
       </c>
       <c r="C12">
-        <v>883.3564565575988</v>
+        <v>877.9694704889887</v>
       </c>
       <c r="D12">
-        <v>826.9464565575988</v>
+        <v>829.4984704889886</v>
       </c>
       <c r="E12">
-        <v>-347.01</v>
+        <v>-339.071</v>
       </c>
       <c r="F12">
-        <v>79.39000000000001</v>
+        <v>87.32900000000001</v>
       </c>
       <c r="G12">
         <v>135.8</v>
@@ -2271,28 +2271,28 @@
         <v>111</v>
       </c>
       <c r="M12">
-        <v>3.993317000000001</v>
+        <v>4.392648700000001</v>
       </c>
       <c r="N12">
-        <v>107.006683</v>
+        <v>106.6073513</v>
       </c>
       <c r="O12">
-        <v>25.68160391999999</v>
+        <v>25.585764312</v>
       </c>
       <c r="P12">
-        <v>81.32507907999999</v>
+        <v>81.021586988</v>
       </c>
       <c r="Q12">
-        <v>193.82507908</v>
+        <v>193.521586988</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1862268554904305</v>
+        <v>0.1874554934782359</v>
       </c>
       <c r="T12">
-        <v>0.6899694058178132</v>
+        <v>0.6960061615327415</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.79644090363975</v>
+        <v>25.26949173058159</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.17104046919563</v>
+        <v>0.1706539684498724</v>
       </c>
       <c r="C13">
-        <v>877.9694704889887</v>
+        <v>872.5982845635363</v>
       </c>
       <c r="D13">
-        <v>829.4984704889886</v>
+        <v>832.0662845635362</v>
       </c>
       <c r="E13">
-        <v>-339.071</v>
+        <v>-331.1320000000001</v>
       </c>
       <c r="F13">
-        <v>87.32900000000001</v>
+        <v>95.268</v>
       </c>
       <c r="G13">
         <v>135.8</v>
@@ -2353,28 +2353,28 @@
         <v>111</v>
       </c>
       <c r="M13">
-        <v>4.392648700000001</v>
+        <v>4.7919804</v>
       </c>
       <c r="N13">
-        <v>106.6073513</v>
+        <v>106.2080196</v>
       </c>
       <c r="O13">
-        <v>25.585764312</v>
+        <v>25.489924704</v>
       </c>
       <c r="P13">
-        <v>81.021586988</v>
+        <v>80.718094896</v>
       </c>
       <c r="Q13">
-        <v>193.521586988</v>
+        <v>193.218094896</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1874554934782359</v>
+        <v>0.1887120550566732</v>
       </c>
       <c r="T13">
-        <v>0.6960061615327415</v>
+        <v>0.7021801162411909</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>25.26949173058159</v>
+        <v>23.16370075303313</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1706539684498724</v>
+        <v>0.1702674677041149</v>
       </c>
       <c r="C14">
-        <v>872.5982845635363</v>
+        <v>867.2430459707176</v>
       </c>
       <c r="D14">
-        <v>832.0662845635362</v>
+        <v>834.6500459707177</v>
       </c>
       <c r="E14">
-        <v>-331.1320000000001</v>
+        <v>-323.193</v>
       </c>
       <c r="F14">
-        <v>95.268</v>
+        <v>103.207</v>
       </c>
       <c r="G14">
         <v>135.8</v>
@@ -2435,28 +2435,28 @@
         <v>111</v>
       </c>
       <c r="M14">
-        <v>4.7919804</v>
+        <v>5.191312100000001</v>
       </c>
       <c r="N14">
-        <v>106.2080196</v>
+        <v>105.8086879</v>
       </c>
       <c r="O14">
-        <v>25.489924704</v>
+        <v>25.39408509599999</v>
       </c>
       <c r="P14">
-        <v>80.718094896</v>
+        <v>80.41460280399998</v>
       </c>
       <c r="Q14">
-        <v>193.218094896</v>
+        <v>192.914602804</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1887120550566732</v>
+        <v>0.1899975031081781</v>
       </c>
       <c r="T14">
-        <v>0.7021801162411909</v>
+        <v>0.7084960009429382</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.16370075303313</v>
+        <v>21.38187761818442</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1702674677041149</v>
+        <v>0.1698809669583574</v>
       </c>
       <c r="C15">
-        <v>867.2430459707176</v>
+        <v>861.9039037339352</v>
       </c>
       <c r="D15">
-        <v>834.6500459707177</v>
+        <v>837.2499037339352</v>
       </c>
       <c r="E15">
-        <v>-323.193</v>
+        <v>-315.254</v>
       </c>
       <c r="F15">
-        <v>103.207</v>
+        <v>111.146</v>
       </c>
       <c r="G15">
         <v>135.8</v>
@@ -2517,28 +2517,28 @@
         <v>111</v>
       </c>
       <c r="M15">
-        <v>5.191312100000001</v>
+        <v>5.590643800000001</v>
       </c>
       <c r="N15">
-        <v>105.8086879</v>
+        <v>105.4093562</v>
       </c>
       <c r="O15">
-        <v>25.39408509599999</v>
+        <v>25.298245488</v>
       </c>
       <c r="P15">
-        <v>80.41460280399998</v>
+        <v>80.111110712</v>
       </c>
       <c r="Q15">
-        <v>192.914602804</v>
+        <v>192.611110712</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1899975031081781</v>
+        <v>0.1913128453004156</v>
       </c>
       <c r="T15">
-        <v>0.7084960009429382</v>
+        <v>0.7149587666842608</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.38187761818442</v>
+        <v>19.85460064545696</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1698809669583574</v>
+        <v>0.1694944662125999</v>
       </c>
       <c r="C16">
-        <v>861.9039037339352</v>
+        <v>856.5810087391696</v>
       </c>
       <c r="D16">
-        <v>837.2499037339352</v>
+        <v>839.8660087391696</v>
       </c>
       <c r="E16">
-        <v>-315.254</v>
+        <v>-307.315</v>
       </c>
       <c r="F16">
-        <v>111.146</v>
+        <v>119.085</v>
       </c>
       <c r="G16">
         <v>135.8</v>
@@ -2599,28 +2599,28 @@
         <v>111</v>
       </c>
       <c r="M16">
-        <v>5.590643800000001</v>
+        <v>5.989975500000002</v>
       </c>
       <c r="N16">
-        <v>105.4093562</v>
+        <v>105.0100245</v>
       </c>
       <c r="O16">
-        <v>25.298245488</v>
+        <v>25.20240588</v>
       </c>
       <c r="P16">
-        <v>80.111110712</v>
+        <v>79.80761861999999</v>
       </c>
       <c r="Q16">
-        <v>192.611110712</v>
+        <v>192.30761862</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1913128453004156</v>
+        <v>0.1926591367207058</v>
       </c>
       <c r="T16">
-        <v>0.7149587666842608</v>
+        <v>0.72157359750185</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.85460064545696</v>
+        <v>18.5309606024265</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1694944662125999</v>
+        <v>0.1691079654668424</v>
       </c>
       <c r="C17">
-        <v>856.5810087391696</v>
+        <v>851.2745137641701</v>
       </c>
       <c r="D17">
-        <v>839.8660087391696</v>
+        <v>842.4985137641702</v>
       </c>
       <c r="E17">
-        <v>-307.3150000000001</v>
+        <v>-299.376</v>
       </c>
       <c r="F17">
-        <v>119.085</v>
+        <v>127.024</v>
       </c>
       <c r="G17">
         <v>135.8</v>
@@ -2681,28 +2681,28 @@
         <v>111</v>
       </c>
       <c r="M17">
-        <v>5.9899755</v>
+        <v>6.3893072</v>
       </c>
       <c r="N17">
-        <v>105.0100245</v>
+        <v>104.6106928</v>
       </c>
       <c r="O17">
-        <v>25.20240588</v>
+        <v>25.10656627199999</v>
       </c>
       <c r="P17">
-        <v>79.80761861999999</v>
+        <v>79.50412652799999</v>
       </c>
       <c r="Q17">
-        <v>192.30761862</v>
+        <v>192.004126528</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1926591367207058</v>
+        <v>0.1940374826986219</v>
       </c>
       <c r="T17">
-        <v>0.7215735975018499</v>
+        <v>0.7283459242912864</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.5309606024265</v>
+        <v>17.37277556477484</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1691079654668424</v>
+        <v>0.1687214647210849</v>
       </c>
       <c r="C18">
-        <v>851.2745137641701</v>
+        <v>845.9845735081972</v>
       </c>
       <c r="D18">
-        <v>842.4985137641702</v>
+        <v>845.1475735081971</v>
       </c>
       <c r="E18">
-        <v>-299.376</v>
+        <v>-291.437</v>
       </c>
       <c r="F18">
-        <v>127.024</v>
+        <v>134.963</v>
       </c>
       <c r="G18">
         <v>135.8</v>
@@ -2763,28 +2763,28 @@
         <v>111</v>
       </c>
       <c r="M18">
-        <v>6.3893072</v>
+        <v>6.7886389</v>
       </c>
       <c r="N18">
-        <v>104.6106928</v>
+        <v>104.2113611</v>
       </c>
       <c r="O18">
-        <v>25.10656627199999</v>
+        <v>25.010726664</v>
       </c>
       <c r="P18">
-        <v>79.50412652799999</v>
+        <v>79.200634436</v>
       </c>
       <c r="Q18">
-        <v>192.004126528</v>
+        <v>191.700634436</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1940374826986219</v>
+        <v>0.1954490418326324</v>
       </c>
       <c r="T18">
-        <v>0.7283459242912864</v>
+        <v>0.7352814396780587</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.37277556477484</v>
+        <v>16.35084759037633</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1687214647210849</v>
+        <v>0.1683349639753274</v>
       </c>
       <c r="C19">
-        <v>845.9845735081972</v>
+        <v>840.7113446223243</v>
       </c>
       <c r="D19">
-        <v>845.1475735081971</v>
+        <v>847.8133446223244</v>
       </c>
       <c r="E19">
-        <v>-291.437</v>
+        <v>-283.498</v>
       </c>
       <c r="F19">
-        <v>134.963</v>
+        <v>142.902</v>
       </c>
       <c r="G19">
         <v>135.8</v>
@@ -2845,28 +2845,28 @@
         <v>111</v>
       </c>
       <c r="M19">
-        <v>6.7886389</v>
+        <v>7.187970600000002</v>
       </c>
       <c r="N19">
-        <v>104.2113611</v>
+        <v>103.8120294</v>
       </c>
       <c r="O19">
-        <v>25.010726664</v>
+        <v>24.91488705599999</v>
       </c>
       <c r="P19">
-        <v>79.200634436</v>
+        <v>78.89714234399999</v>
       </c>
       <c r="Q19">
-        <v>191.700634436</v>
+        <v>191.397142344</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1954490418326324</v>
+        <v>0.1968950292382041</v>
       </c>
       <c r="T19">
-        <v>0.7352814396780587</v>
+        <v>0.7423861139767035</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.35084759037633</v>
+        <v>15.44246716868875</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1683349639753274</v>
+        <v>0.1679484632295698</v>
       </c>
       <c r="C20">
-        <v>840.7113446223243</v>
+        <v>835.4549857403209</v>
       </c>
       <c r="D20">
-        <v>847.8133446223244</v>
+        <v>850.4959857403209</v>
       </c>
       <c r="E20">
-        <v>-283.498</v>
+        <v>-275.559</v>
       </c>
       <c r="F20">
-        <v>142.902</v>
+        <v>150.841</v>
       </c>
       <c r="G20">
         <v>135.8</v>
@@ -2927,28 +2927,28 @@
         <v>111</v>
       </c>
       <c r="M20">
-        <v>7.187970600000001</v>
+        <v>7.5873023</v>
       </c>
       <c r="N20">
-        <v>103.8120294</v>
+        <v>103.4126977</v>
       </c>
       <c r="O20">
-        <v>24.91488705599999</v>
+        <v>24.819047448</v>
       </c>
       <c r="P20">
-        <v>78.89714234399999</v>
+        <v>78.59365025199999</v>
       </c>
       <c r="Q20">
-        <v>191.397142344</v>
+        <v>191.093650252</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1968950292382041</v>
+        <v>0.198376720036506</v>
       </c>
       <c r="T20">
-        <v>0.7423861139767033</v>
+        <v>0.7496662123321047</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.44246716868875</v>
+        <v>14.62970573875776</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1679484632295698</v>
+        <v>0.1675619624838124</v>
       </c>
       <c r="C21">
-        <v>835.4549857403209</v>
+        <v>830.2156575101158</v>
       </c>
       <c r="D21">
-        <v>850.4959857403209</v>
+        <v>853.1956575101158</v>
       </c>
       <c r="E21">
-        <v>-275.559</v>
+        <v>-267.62</v>
       </c>
       <c r="F21">
-        <v>150.841</v>
+        <v>158.78</v>
       </c>
       <c r="G21">
         <v>135.8</v>
@@ -3009,28 +3009,28 @@
         <v>111</v>
       </c>
       <c r="M21">
-        <v>7.5873023</v>
+        <v>7.986634000000001</v>
       </c>
       <c r="N21">
-        <v>103.4126977</v>
+        <v>103.013366</v>
       </c>
       <c r="O21">
-        <v>24.819047448</v>
+        <v>24.72320784</v>
       </c>
       <c r="P21">
-        <v>78.59365025199999</v>
+        <v>78.29015815999999</v>
       </c>
       <c r="Q21">
-        <v>191.093650252</v>
+        <v>190.79015816</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.198376720036506</v>
+        <v>0.1998954531047654</v>
       </c>
       <c r="T21">
-        <v>0.7496662123321047</v>
+        <v>0.7571283131463912</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.62970573875776</v>
+        <v>13.89822045181987</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1675619624838124</v>
+        <v>0.1671754617380549</v>
       </c>
       <c r="C22">
-        <v>830.2156575101158</v>
+        <v>824.9935226258704</v>
       </c>
       <c r="D22">
-        <v>853.1956575101158</v>
+        <v>855.9125226258703</v>
       </c>
       <c r="E22">
-        <v>-267.62</v>
+        <v>-259.681</v>
       </c>
       <c r="F22">
-        <v>158.78</v>
+        <v>166.719</v>
       </c>
       <c r="G22">
         <v>135.8</v>
@@ -3091,28 +3091,28 @@
         <v>111</v>
       </c>
       <c r="M22">
-        <v>7.986634000000001</v>
+        <v>8.3859657</v>
       </c>
       <c r="N22">
-        <v>103.013366</v>
+        <v>102.6140343</v>
       </c>
       <c r="O22">
-        <v>24.72320784</v>
+        <v>24.62736823199999</v>
       </c>
       <c r="P22">
-        <v>78.29015815999999</v>
+        <v>77.98666606799999</v>
       </c>
       <c r="Q22">
-        <v>190.79015816</v>
+        <v>190.486666068</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1998954531047654</v>
+        <v>0.2014526351114618</v>
       </c>
       <c r="T22">
-        <v>0.7571283131463912</v>
+        <v>0.7647793279053432</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.89822045181987</v>
+        <v>13.23640043030464</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1671754617380548</v>
+        <v>0.1670397609922973</v>
       </c>
       <c r="C23">
-        <v>824.9935226258704</v>
+        <v>818.0125249072418</v>
       </c>
       <c r="D23">
-        <v>855.9125226258705</v>
+        <v>856.8705249072417</v>
       </c>
       <c r="E23">
-        <v>-259.681</v>
+        <v>-251.742</v>
       </c>
       <c r="F23">
-        <v>166.719</v>
+        <v>174.658</v>
       </c>
       <c r="G23">
         <v>135.8</v>
@@ -3173,45 +3173,45 @@
         <v>111</v>
       </c>
       <c r="M23">
-        <v>8.3859657</v>
+        <v>9.047284400000001</v>
       </c>
       <c r="N23">
-        <v>102.6140343</v>
+        <v>101.9527156</v>
       </c>
       <c r="O23">
-        <v>24.62736823199999</v>
+        <v>24.468651744</v>
       </c>
       <c r="P23">
-        <v>77.98666606799999</v>
+        <v>77.48406385599999</v>
       </c>
       <c r="Q23">
-        <v>190.486666068</v>
+        <v>189.984063856</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2014526351114618</v>
+        <v>0.2030497448619197</v>
       </c>
       <c r="T23">
-        <v>0.7647793279053432</v>
+        <v>0.7726265225299094</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.24</v>
       </c>
       <c r="W23">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.23640043030464</v>
+        <v>12.26887484602562</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1670397609922973</v>
+        <v>0.1666646602465398</v>
       </c>
       <c r="C24">
-        <v>818.0125249072418</v>
+        <v>812.7328032459613</v>
       </c>
       <c r="D24">
-        <v>856.8705249072417</v>
+        <v>859.5298032459613</v>
       </c>
       <c r="E24">
-        <v>-251.742</v>
+        <v>-243.803</v>
       </c>
       <c r="F24">
-        <v>174.658</v>
+        <v>182.597</v>
       </c>
       <c r="G24">
         <v>135.8</v>
@@ -3255,28 +3255,28 @@
         <v>111</v>
       </c>
       <c r="M24">
-        <v>9.047284400000001</v>
+        <v>9.458524600000002</v>
       </c>
       <c r="N24">
-        <v>101.9527156</v>
+        <v>101.5414754</v>
       </c>
       <c r="O24">
-        <v>24.468651744</v>
+        <v>24.36995409599999</v>
       </c>
       <c r="P24">
-        <v>77.48406385599999</v>
+        <v>77.17152130399998</v>
       </c>
       <c r="Q24">
-        <v>189.984063856</v>
+        <v>189.671521304</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2030497448619197</v>
+        <v>0.2046883379825193</v>
       </c>
       <c r="T24">
-        <v>0.7726265225299094</v>
+        <v>0.7806775403914772</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.26887484602562</v>
+        <v>11.73544550489407</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1666646602465398</v>
+        <v>0.1662895595007823</v>
       </c>
       <c r="C25">
-        <v>812.7328032459613</v>
+        <v>807.4696389908524</v>
       </c>
       <c r="D25">
-        <v>859.5298032459613</v>
+        <v>862.2056389908524</v>
       </c>
       <c r="E25">
-        <v>-243.803</v>
+        <v>-235.864</v>
       </c>
       <c r="F25">
-        <v>182.597</v>
+        <v>190.536</v>
       </c>
       <c r="G25">
         <v>135.8</v>
@@ -3337,28 +3337,28 @@
         <v>111</v>
       </c>
       <c r="M25">
-        <v>9.458524600000002</v>
+        <v>9.8697648</v>
       </c>
       <c r="N25">
-        <v>101.5414754</v>
+        <v>101.1302352</v>
       </c>
       <c r="O25">
-        <v>24.36995409599999</v>
+        <v>24.271256448</v>
       </c>
       <c r="P25">
-        <v>77.17152130399998</v>
+        <v>76.85897875199998</v>
       </c>
       <c r="Q25">
-        <v>189.671521304</v>
+        <v>189.358978752</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2046883379825193</v>
+        <v>0.2063700519747136</v>
       </c>
       <c r="T25">
-        <v>0.7806775403914772</v>
+        <v>0.7889404271441388</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.73544550489407</v>
+        <v>11.24646860885682</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1662895595007823</v>
+        <v>0.1659144587550248</v>
       </c>
       <c r="C26">
-        <v>807.4696389908524</v>
+        <v>802.2231872613435</v>
       </c>
       <c r="D26">
-        <v>862.2056389908524</v>
+        <v>864.8981872613435</v>
       </c>
       <c r="E26">
-        <v>-235.864</v>
+        <v>-227.925</v>
       </c>
       <c r="F26">
-        <v>190.536</v>
+        <v>198.475</v>
       </c>
       <c r="G26">
         <v>135.8</v>
@@ -3419,28 +3419,28 @@
         <v>111</v>
       </c>
       <c r="M26">
-        <v>9.8697648</v>
+        <v>10.281005</v>
       </c>
       <c r="N26">
-        <v>101.1302352</v>
+        <v>100.718995</v>
       </c>
       <c r="O26">
-        <v>24.271256448</v>
+        <v>24.17255879999999</v>
       </c>
       <c r="P26">
-        <v>76.85897875199998</v>
+        <v>76.54643619999999</v>
       </c>
       <c r="Q26">
-        <v>189.358978752</v>
+        <v>189.0464362</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2063700519747136</v>
+        <v>0.2080966116733664</v>
       </c>
       <c r="T26">
-        <v>0.7889404271441388</v>
+        <v>0.7974236575435382</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.24646860885682</v>
+        <v>10.79660986450254</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1659144587550248</v>
+        <v>0.1655393580092673</v>
       </c>
       <c r="C27">
-        <v>802.2231872613435</v>
+        <v>796.9936051205984</v>
       </c>
       <c r="D27">
-        <v>864.8981872613435</v>
+        <v>867.6076051205985</v>
       </c>
       <c r="E27">
-        <v>-227.925</v>
+        <v>-219.986</v>
       </c>
       <c r="F27">
-        <v>198.475</v>
+        <v>206.414</v>
       </c>
       <c r="G27">
         <v>135.8</v>
@@ -3501,28 +3501,28 @@
         <v>111</v>
       </c>
       <c r="M27">
-        <v>10.281005</v>
+        <v>10.6922452</v>
       </c>
       <c r="N27">
-        <v>100.718995</v>
+        <v>100.3077548</v>
       </c>
       <c r="O27">
-        <v>24.17255879999999</v>
+        <v>24.073861152</v>
       </c>
       <c r="P27">
-        <v>76.54643619999999</v>
+        <v>76.23389364799999</v>
       </c>
       <c r="Q27">
-        <v>189.0464362</v>
+        <v>188.733893648</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2080966116733664</v>
+        <v>0.2098698351476585</v>
       </c>
       <c r="T27">
-        <v>0.7974236575435382</v>
+        <v>0.8061361644402185</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.79660986450254</v>
+        <v>10.38135563894475</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1655393580092673</v>
+        <v>0.1651642572635098</v>
       </c>
       <c r="C28">
-        <v>796.9936051205984</v>
+        <v>791.7810516060581</v>
       </c>
       <c r="D28">
-        <v>867.6076051205985</v>
+        <v>870.3340516060582</v>
       </c>
       <c r="E28">
-        <v>-219.986</v>
+        <v>-212.047</v>
       </c>
       <c r="F28">
-        <v>206.414</v>
+        <v>214.353</v>
       </c>
       <c r="G28">
         <v>135.8</v>
@@ -3583,28 +3583,28 @@
         <v>111</v>
       </c>
       <c r="M28">
-        <v>10.6922452</v>
+        <v>11.1034854</v>
       </c>
       <c r="N28">
-        <v>100.3077548</v>
+        <v>99.89651459999999</v>
       </c>
       <c r="O28">
-        <v>24.073861152</v>
+        <v>23.975163504</v>
       </c>
       <c r="P28">
-        <v>76.23389364799999</v>
+        <v>75.921351096</v>
       </c>
       <c r="Q28">
-        <v>188.733893648</v>
+        <v>188.421351096</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2098698351476585</v>
+        <v>0.2116916400869997</v>
       </c>
       <c r="T28">
-        <v>0.8061361644402185</v>
+        <v>0.8150873701559861</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.38135563894475</v>
+        <v>9.996860985650503</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1651642572635098</v>
+        <v>0.1651509165177523</v>
       </c>
       <c r="C29">
-        <v>791.7810516060581</v>
+        <v>783.9393353609329</v>
       </c>
       <c r="D29">
-        <v>870.3340516060582</v>
+        <v>870.431335360933</v>
       </c>
       <c r="E29">
-        <v>-212.047</v>
+        <v>-204.108</v>
       </c>
       <c r="F29">
-        <v>214.353</v>
+        <v>222.2920000000001</v>
       </c>
       <c r="G29">
         <v>135.8</v>
@@ -3665,45 +3665,45 @@
         <v>111</v>
       </c>
       <c r="M29">
-        <v>11.1034854</v>
+        <v>11.892622</v>
       </c>
       <c r="N29">
-        <v>99.89651459999999</v>
+        <v>99.10737799999998</v>
       </c>
       <c r="O29">
-        <v>23.975163504</v>
+        <v>23.78577072</v>
       </c>
       <c r="P29">
-        <v>75.921351096</v>
+        <v>75.32160727999999</v>
       </c>
       <c r="Q29">
-        <v>188.421351096</v>
+        <v>187.82160728</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2116916400869997</v>
+        <v>0.2135640507191004</v>
       </c>
       <c r="T29">
-        <v>0.8150873701559861</v>
+        <v>0.8242872204749694</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.24</v>
       </c>
       <c r="W29">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>9.996860985650503</v>
+        <v>9.333517873518552</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1651509165177523</v>
+        <v>0.1647887357719948</v>
       </c>
       <c r="C30">
-        <v>783.9393353609329</v>
+        <v>778.6497749749128</v>
       </c>
       <c r="D30">
-        <v>870.431335360933</v>
+        <v>873.0807749749129</v>
       </c>
       <c r="E30">
-        <v>-204.108</v>
+        <v>-196.169</v>
       </c>
       <c r="F30">
-        <v>222.2920000000001</v>
+        <v>230.2310000000001</v>
       </c>
       <c r="G30">
         <v>135.8</v>
@@ -3747,28 +3747,28 @@
         <v>111</v>
       </c>
       <c r="M30">
-        <v>11.892622</v>
+        <v>12.3173585</v>
       </c>
       <c r="N30">
-        <v>99.10737799999998</v>
+        <v>98.68264149999999</v>
       </c>
       <c r="O30">
-        <v>23.78577072</v>
+        <v>23.68383396</v>
       </c>
       <c r="P30">
-        <v>75.32160727999999</v>
+        <v>74.99880753999999</v>
       </c>
       <c r="Q30">
-        <v>187.82160728</v>
+        <v>187.49880754</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2135640507191004</v>
+        <v>0.2154892053126687</v>
       </c>
       <c r="T30">
-        <v>0.8242872204749694</v>
+        <v>0.8337462215071636</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.333517873518552</v>
+        <v>9.01167242960412</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1647887357719948</v>
+        <v>0.1644265550262372</v>
       </c>
       <c r="C31">
-        <v>778.6497749749128</v>
+        <v>773.3763926868753</v>
       </c>
       <c r="D31">
-        <v>873.0807749749129</v>
+        <v>875.7463926868753</v>
       </c>
       <c r="E31">
-        <v>-196.169</v>
+        <v>-188.23</v>
       </c>
       <c r="F31">
-        <v>230.231</v>
+        <v>238.17</v>
       </c>
       <c r="G31">
         <v>135.8</v>
@@ -3829,28 +3829,28 @@
         <v>111</v>
       </c>
       <c r="M31">
-        <v>12.3173585</v>
+        <v>12.742095</v>
       </c>
       <c r="N31">
-        <v>98.68264149999999</v>
+        <v>98.25790499999998</v>
       </c>
       <c r="O31">
-        <v>23.68383396</v>
+        <v>23.58189719999999</v>
       </c>
       <c r="P31">
-        <v>74.99880753999999</v>
+        <v>74.67600779999998</v>
       </c>
       <c r="Q31">
-        <v>187.49880754</v>
+        <v>187.1760078</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2154892053126687</v>
+        <v>0.2174693643231961</v>
       </c>
       <c r="T31">
-        <v>0.8337462215071636</v>
+        <v>0.8434754797117059</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.011672429604122</v>
+        <v>8.711283348617318</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1644265550262372</v>
+        <v>0.1640643742804797</v>
       </c>
       <c r="C32">
-        <v>773.3763926868753</v>
+        <v>768.1193371314934</v>
       </c>
       <c r="D32">
-        <v>875.7463926868753</v>
+        <v>878.4283371314933</v>
       </c>
       <c r="E32">
-        <v>-188.23</v>
+        <v>-180.291</v>
       </c>
       <c r="F32">
-        <v>238.17</v>
+        <v>246.109</v>
       </c>
       <c r="G32">
         <v>135.8</v>
@@ -3911,28 +3911,28 @@
         <v>111</v>
       </c>
       <c r="M32">
-        <v>12.742095</v>
+        <v>13.1668315</v>
       </c>
       <c r="N32">
-        <v>98.25790499999998</v>
+        <v>97.83316849999999</v>
       </c>
       <c r="O32">
-        <v>23.58189719999999</v>
+        <v>23.47996044</v>
       </c>
       <c r="P32">
-        <v>74.67600779999998</v>
+        <v>74.35320805999999</v>
       </c>
       <c r="Q32">
-        <v>187.1760078</v>
+        <v>186.85320806</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2174693643231961</v>
+        <v>0.2195069192470721</v>
       </c>
       <c r="T32">
-        <v>0.8434754797117059</v>
+        <v>0.8534867454004381</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.711283348617318</v>
+        <v>8.430274208339338</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1640643742804797</v>
+        <v>0.1637021935347222</v>
       </c>
       <c r="C33">
-        <v>768.1193371314934</v>
+        <v>762.8787587697907</v>
       </c>
       <c r="D33">
-        <v>878.4283371314933</v>
+        <v>881.1267587697906</v>
       </c>
       <c r="E33">
-        <v>-180.291</v>
+        <v>-172.352</v>
       </c>
       <c r="F33">
-        <v>246.109</v>
+        <v>254.048</v>
       </c>
       <c r="G33">
         <v>135.8</v>
@@ -3993,28 +3993,28 @@
         <v>111</v>
       </c>
       <c r="M33">
-        <v>13.1668315</v>
+        <v>13.591568</v>
       </c>
       <c r="N33">
-        <v>97.83316849999999</v>
+        <v>97.40843199999999</v>
       </c>
       <c r="O33">
-        <v>23.47996044</v>
+        <v>23.37802368</v>
       </c>
       <c r="P33">
-        <v>74.35320805999999</v>
+        <v>74.03040831999999</v>
       </c>
       <c r="Q33">
-        <v>186.85320806</v>
+        <v>186.53040832</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2195069192470721</v>
+        <v>0.2216044022569444</v>
       </c>
       <c r="T33">
-        <v>0.8534867454004381</v>
+        <v>0.8637924600800153</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.430274208339338</v>
+        <v>8.166828139328736</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1637021935347222</v>
+        <v>0.1633400127889647</v>
       </c>
       <c r="C34">
-        <v>762.8787587697907</v>
+        <v>757.654809917276</v>
       </c>
       <c r="D34">
-        <v>881.1267587697906</v>
+        <v>883.841809917276</v>
       </c>
       <c r="E34">
-        <v>-172.352</v>
+        <v>-164.413</v>
       </c>
       <c r="F34">
-        <v>254.048</v>
+        <v>261.987</v>
       </c>
       <c r="G34">
         <v>135.8</v>
@@ -4075,28 +4075,28 @@
         <v>111</v>
       </c>
       <c r="M34">
-        <v>13.591568</v>
+        <v>14.0163045</v>
       </c>
       <c r="N34">
-        <v>97.40843199999999</v>
+        <v>96.98369549999998</v>
       </c>
       <c r="O34">
-        <v>23.37802368</v>
+        <v>23.27608691999999</v>
       </c>
       <c r="P34">
-        <v>74.03040831999999</v>
+        <v>73.70760857999998</v>
       </c>
       <c r="Q34">
-        <v>186.53040832</v>
+        <v>186.20760858</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2216044022569444</v>
+        <v>0.2237644966999473</v>
       </c>
       <c r="T34">
-        <v>0.8637924600800153</v>
+        <v>0.8744058080336098</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.166828139328736</v>
+        <v>7.919348498743016</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1633400127889647</v>
+        <v>0.1629778320432072</v>
       </c>
       <c r="C35">
-        <v>757.654809917276</v>
+        <v>752.4476447726048</v>
       </c>
       <c r="D35">
-        <v>883.841809917276</v>
+        <v>886.5736447726048</v>
       </c>
       <c r="E35">
-        <v>-164.413</v>
+        <v>-156.474</v>
       </c>
       <c r="F35">
-        <v>261.987</v>
+        <v>269.926</v>
       </c>
       <c r="G35">
         <v>135.8</v>
@@ -4157,28 +4157,28 @@
         <v>111</v>
       </c>
       <c r="M35">
-        <v>14.0163045</v>
+        <v>14.441041</v>
       </c>
       <c r="N35">
-        <v>96.98369549999998</v>
+        <v>96.55895899999999</v>
       </c>
       <c r="O35">
-        <v>23.27608691999999</v>
+        <v>23.17415016</v>
       </c>
       <c r="P35">
-        <v>73.70760857999998</v>
+        <v>73.38480883999999</v>
       </c>
       <c r="Q35">
-        <v>186.20760858</v>
+        <v>185.88480884</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2237644966999473</v>
+        <v>0.225990048550314</v>
       </c>
       <c r="T35">
-        <v>0.8744058080336098</v>
+        <v>0.8853407725918586</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.919348498743016</v>
+        <v>7.686426484074103</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1629778320432072</v>
+        <v>0.1628284512974497</v>
       </c>
       <c r="C36">
-        <v>752.4476447726048</v>
+        <v>745.640310027992</v>
       </c>
       <c r="D36">
-        <v>886.5736447726048</v>
+        <v>887.7053100279919</v>
       </c>
       <c r="E36">
-        <v>-156.474</v>
+        <v>-148.535</v>
       </c>
       <c r="F36">
-        <v>269.926</v>
+        <v>277.8650000000001</v>
       </c>
       <c r="G36">
         <v>135.8</v>
@@ -4239,45 +4239,45 @@
         <v>111</v>
       </c>
       <c r="M36">
-        <v>14.441041</v>
+        <v>15.0880695</v>
       </c>
       <c r="N36">
-        <v>96.55895899999999</v>
+        <v>95.91193049999998</v>
       </c>
       <c r="O36">
-        <v>23.17415016</v>
+        <v>23.01886331999999</v>
       </c>
       <c r="P36">
-        <v>73.38480883999999</v>
+        <v>72.89306717999999</v>
       </c>
       <c r="Q36">
-        <v>185.88480884</v>
+        <v>185.39306718</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.225990048550314</v>
+        <v>0.2282840789191534</v>
       </c>
       <c r="T36">
-        <v>0.8853407725918586</v>
+        <v>0.8966121975980536</v>
       </c>
       <c r="U36">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.24</v>
       </c>
       <c r="W36">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>7.686426484074103</v>
+        <v>7.356805985020149</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1628284512974497</v>
+        <v>0.1624723505516922</v>
       </c>
       <c r="C37">
-        <v>745.640310027992</v>
+        <v>740.4107139391938</v>
       </c>
       <c r="D37">
-        <v>887.7053100279919</v>
+        <v>890.4147139391939</v>
       </c>
       <c r="E37">
-        <v>-148.535</v>
+        <v>-140.5959999999999</v>
       </c>
       <c r="F37">
-        <v>277.8650000000001</v>
+        <v>285.8040000000001</v>
       </c>
       <c r="G37">
         <v>135.8</v>
@@ -4321,28 +4321,28 @@
         <v>111</v>
       </c>
       <c r="M37">
-        <v>15.0880695</v>
+        <v>15.51915720000001</v>
       </c>
       <c r="N37">
-        <v>95.91193049999998</v>
+        <v>95.48084279999998</v>
       </c>
       <c r="O37">
-        <v>23.01886331999999</v>
+        <v>22.91540227199999</v>
       </c>
       <c r="P37">
-        <v>72.89306717999999</v>
+        <v>72.56544052799998</v>
       </c>
       <c r="Q37">
-        <v>185.39306718</v>
+        <v>185.065440528</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2282840789191534</v>
+        <v>0.230649797737019</v>
       </c>
       <c r="T37">
-        <v>0.8966121975980536</v>
+        <v>0.9082358546356921</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.356805985020149</v>
+        <v>7.152450263214032</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1624723505516922</v>
+        <v>0.1621162498059347</v>
       </c>
       <c r="C38">
-        <v>740.4107139391938</v>
+        <v>735.1977074628522</v>
       </c>
       <c r="D38">
-        <v>890.4147139391939</v>
+        <v>893.1407074628522</v>
       </c>
       <c r="E38">
-        <v>-140.596</v>
+        <v>-132.657</v>
       </c>
       <c r="F38">
-        <v>285.804</v>
+        <v>293.7430000000001</v>
       </c>
       <c r="G38">
         <v>135.8</v>
@@ -4403,28 +4403,28 @@
         <v>111</v>
       </c>
       <c r="M38">
-        <v>15.5191572</v>
+        <v>15.9502449</v>
       </c>
       <c r="N38">
-        <v>95.48084279999998</v>
+        <v>95.04975509999998</v>
       </c>
       <c r="O38">
-        <v>22.91540227199999</v>
+        <v>22.81194122399999</v>
       </c>
       <c r="P38">
-        <v>72.56544052799998</v>
+        <v>72.23781387599999</v>
       </c>
       <c r="Q38">
-        <v>185.065440528</v>
+        <v>184.737813876</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.230649797737019</v>
+        <v>0.2330906187395788</v>
       </c>
       <c r="T38">
-        <v>0.908235854635692</v>
+        <v>0.9202285166586524</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.152450263214034</v>
+        <v>6.959140796640681</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1621162498059347</v>
+        <v>0.1617601490601772</v>
       </c>
       <c r="C39">
-        <v>735.1977074628522</v>
+        <v>730.0014434335421</v>
       </c>
       <c r="D39">
-        <v>893.1407074628522</v>
+        <v>895.8834434335421</v>
       </c>
       <c r="E39">
-        <v>-132.657</v>
+        <v>-124.718</v>
       </c>
       <c r="F39">
-        <v>293.7430000000001</v>
+        <v>301.682</v>
       </c>
       <c r="G39">
         <v>135.8</v>
@@ -4485,28 +4485,28 @@
         <v>111</v>
       </c>
       <c r="M39">
-        <v>15.9502449</v>
+        <v>16.3813326</v>
       </c>
       <c r="N39">
-        <v>95.04975509999998</v>
+        <v>94.61866739999999</v>
       </c>
       <c r="O39">
-        <v>22.81194122399999</v>
+        <v>22.708480176</v>
       </c>
       <c r="P39">
-        <v>72.23781387599999</v>
+        <v>71.910187224</v>
       </c>
       <c r="Q39">
-        <v>184.737813876</v>
+        <v>184.410187224</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2330906187395788</v>
+        <v>0.2356101759035115</v>
       </c>
       <c r="T39">
-        <v>0.9202285166586524</v>
+        <v>0.9326080387468696</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.959140796640681</v>
+        <v>6.77600551251856</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1617601490601772</v>
+        <v>0.1614040483144197</v>
       </c>
       <c r="C40">
-        <v>730.0014434335421</v>
+        <v>724.8220765689734</v>
       </c>
       <c r="D40">
-        <v>895.8834434335421</v>
+        <v>898.6430765689736</v>
       </c>
       <c r="E40">
-        <v>-124.718</v>
+        <v>-116.779</v>
       </c>
       <c r="F40">
-        <v>301.682</v>
+        <v>309.621</v>
       </c>
       <c r="G40">
         <v>135.8</v>
@@ -4567,28 +4567,28 @@
         <v>111</v>
       </c>
       <c r="M40">
-        <v>16.3813326</v>
+        <v>16.8124203</v>
       </c>
       <c r="N40">
-        <v>94.61866739999999</v>
+        <v>94.18757969999999</v>
       </c>
       <c r="O40">
-        <v>22.708480176</v>
+        <v>22.605019128</v>
       </c>
       <c r="P40">
-        <v>71.910187224</v>
+        <v>71.58256057199999</v>
       </c>
       <c r="Q40">
-        <v>184.410187224</v>
+        <v>184.082560572</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2356101759035115</v>
+        <v>0.2382123414990486</v>
       </c>
       <c r="T40">
-        <v>0.9326080387468696</v>
+        <v>0.9453934468051922</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.77600551251856</v>
+        <v>6.602261781428339</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1614040483144197</v>
+        <v>0.1610479475686621</v>
       </c>
       <c r="C41">
-        <v>724.8220765689734</v>
+        <v>719.6597634990845</v>
       </c>
       <c r="D41">
-        <v>898.6430765689736</v>
+        <v>901.4197634990846</v>
       </c>
       <c r="E41">
-        <v>-116.779</v>
+        <v>-108.84</v>
       </c>
       <c r="F41">
-        <v>309.621</v>
+        <v>317.5600000000001</v>
       </c>
       <c r="G41">
         <v>135.8</v>
@@ -4649,28 +4649,28 @@
         <v>111</v>
       </c>
       <c r="M41">
-        <v>16.8124203</v>
+        <v>17.243508</v>
       </c>
       <c r="N41">
-        <v>94.18757969999999</v>
+        <v>93.75649199999998</v>
       </c>
       <c r="O41">
-        <v>22.605019128</v>
+        <v>22.50155808</v>
       </c>
       <c r="P41">
-        <v>71.58256057199999</v>
+        <v>71.25493391999998</v>
       </c>
       <c r="Q41">
-        <v>184.082560572</v>
+        <v>183.75493392</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2382123414990486</v>
+        <v>0.2409012459477703</v>
       </c>
       <c r="T41">
-        <v>0.9453934468051922</v>
+        <v>0.9586050351321257</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.602261781428339</v>
+        <v>6.43720523689263</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1610479475686621</v>
+        <v>0.1606918468229046</v>
       </c>
       <c r="C42">
-        <v>719.6597634990845</v>
+        <v>714.5146627956763</v>
       </c>
       <c r="D42">
-        <v>901.4197634990846</v>
+        <v>904.2136627956762</v>
       </c>
       <c r="E42">
-        <v>-108.84</v>
+        <v>-100.901</v>
       </c>
       <c r="F42">
-        <v>317.5600000000001</v>
+        <v>325.4990000000001</v>
       </c>
       <c r="G42">
         <v>135.8</v>
@@ -4731,28 +4731,28 @@
         <v>111</v>
       </c>
       <c r="M42">
-        <v>17.243508</v>
+        <v>17.6745957</v>
       </c>
       <c r="N42">
-        <v>93.75649199999998</v>
+        <v>93.32540429999997</v>
       </c>
       <c r="O42">
-        <v>22.50155808</v>
+        <v>22.39809703199999</v>
       </c>
       <c r="P42">
-        <v>71.25493391999998</v>
+        <v>70.92730726799998</v>
       </c>
       <c r="Q42">
-        <v>183.75493392</v>
+        <v>183.427307268</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2409012459477703</v>
+        <v>0.2436812996998383</v>
       </c>
       <c r="T42">
-        <v>0.9586050351321257</v>
+        <v>0.9722644739108194</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.43720523689263</v>
+        <v>6.28020023111476</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1606918468229046</v>
+        <v>0.1603357460771471</v>
       </c>
       <c r="C43">
-        <v>714.5146627956763</v>
+        <v>709.3869350025971</v>
       </c>
       <c r="D43">
-        <v>904.2136627956762</v>
+        <v>907.0249350025971</v>
       </c>
       <c r="E43">
-        <v>-100.901</v>
+        <v>-92.96199999999999</v>
       </c>
       <c r="F43">
-        <v>325.4990000000001</v>
+        <v>333.438</v>
       </c>
       <c r="G43">
         <v>135.8</v>
@@ -4813,28 +4813,28 @@
         <v>111</v>
       </c>
       <c r="M43">
-        <v>17.6745957</v>
+        <v>18.1056834</v>
       </c>
       <c r="N43">
-        <v>93.32540429999997</v>
+        <v>92.89431659999998</v>
       </c>
       <c r="O43">
-        <v>22.39809703199999</v>
+        <v>22.294635984</v>
       </c>
       <c r="P43">
-        <v>70.92730726799998</v>
+        <v>70.59968061599999</v>
       </c>
       <c r="Q43">
-        <v>183.427307268</v>
+        <v>183.099680616</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2436812996998383</v>
+        <v>0.2465572173743916</v>
       </c>
       <c r="T43">
-        <v>0.9722644739108194</v>
+        <v>0.9863949278198132</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.28020023111476</v>
+        <v>6.130671654183457</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1603357460771471</v>
+        <v>0.1603064453313896</v>
       </c>
       <c r="C44">
-        <v>709.3869350025971</v>
+        <v>701.6800311692305</v>
       </c>
       <c r="D44">
-        <v>907.0249350025971</v>
+        <v>907.2570311692303</v>
       </c>
       <c r="E44">
-        <v>-92.96199999999999</v>
+        <v>-85.02300000000002</v>
       </c>
       <c r="F44">
-        <v>333.438</v>
+        <v>341.377</v>
       </c>
       <c r="G44">
         <v>135.8</v>
@@ -4895,45 +4895,45 @@
         <v>111</v>
       </c>
       <c r="M44">
-        <v>18.1056834</v>
+        <v>18.8781481</v>
       </c>
       <c r="N44">
-        <v>92.89431659999998</v>
+        <v>92.12185189999998</v>
       </c>
       <c r="O44">
-        <v>22.294635984</v>
+        <v>22.109244456</v>
       </c>
       <c r="P44">
-        <v>70.59968061599999</v>
+        <v>70.01260744399998</v>
       </c>
       <c r="Q44">
-        <v>183.099680616</v>
+        <v>182.512607444</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2465572173743916</v>
+        <v>0.2495340444410344</v>
       </c>
       <c r="T44">
-        <v>0.9863949278198131</v>
+        <v>1.001021187129122</v>
       </c>
       <c r="U44">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.24</v>
       </c>
       <c r="W44">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>6.130671654183457</v>
+        <v>5.879814026885401</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1603064453313896</v>
+        <v>0.1599579445856321</v>
       </c>
       <c r="C45">
-        <v>701.6800311692305</v>
+        <v>696.5107004472111</v>
       </c>
       <c r="D45">
-        <v>907.2570311692303</v>
+        <v>910.0267004472112</v>
       </c>
       <c r="E45">
-        <v>-85.02300000000002</v>
+        <v>-77.084</v>
       </c>
       <c r="F45">
-        <v>341.377</v>
+        <v>349.316</v>
       </c>
       <c r="G45">
         <v>135.8</v>
@@ -4977,28 +4977,28 @@
         <v>111</v>
       </c>
       <c r="M45">
-        <v>18.8781481</v>
+        <v>19.3171748</v>
       </c>
       <c r="N45">
-        <v>92.12185189999998</v>
+        <v>91.68282519999998</v>
       </c>
       <c r="O45">
-        <v>22.109244456</v>
+        <v>22.00387804799999</v>
       </c>
       <c r="P45">
-        <v>70.01260744399998</v>
+        <v>69.67894715199999</v>
       </c>
       <c r="Q45">
-        <v>182.512607444</v>
+        <v>182.178947152</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2495340444410344</v>
+        <v>0.2526171867600573</v>
       </c>
       <c r="T45">
-        <v>1.001021187129122</v>
+        <v>1.016169812842335</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.879814026885401</v>
+        <v>5.746181889910732</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1599579445856321</v>
+        <v>0.1596094438398746</v>
       </c>
       <c r="C46">
-        <v>696.5107004472111</v>
+        <v>691.3583319697348</v>
       </c>
       <c r="D46">
-        <v>910.0267004472112</v>
+        <v>912.8133319697348</v>
       </c>
       <c r="E46">
-        <v>-77.084</v>
+        <v>-69.14499999999998</v>
       </c>
       <c r="F46">
-        <v>349.316</v>
+        <v>357.2550000000001</v>
       </c>
       <c r="G46">
         <v>135.8</v>
@@ -5059,28 +5059,28 @@
         <v>111</v>
       </c>
       <c r="M46">
-        <v>19.3171748</v>
+        <v>19.7562015</v>
       </c>
       <c r="N46">
-        <v>91.68282519999998</v>
+        <v>91.24379849999998</v>
       </c>
       <c r="O46">
-        <v>22.00387804799999</v>
+        <v>21.89851164</v>
       </c>
       <c r="P46">
-        <v>69.67894715199999</v>
+        <v>69.34528685999999</v>
       </c>
       <c r="Q46">
-        <v>182.178947152</v>
+        <v>181.84528686</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2526171867600573</v>
+        <v>0.2558124433452265</v>
       </c>
       <c r="T46">
-        <v>1.016169812842335</v>
+        <v>1.031869297672393</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.746181889910732</v>
+        <v>5.618488959023827</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1596094438398746</v>
+        <v>0.1592609430941171</v>
       </c>
       <c r="C47">
-        <v>691.3583319697348</v>
+        <v>686.2230820378528</v>
       </c>
       <c r="D47">
-        <v>912.8133319697348</v>
+        <v>915.6170820378529</v>
       </c>
       <c r="E47">
-        <v>-69.14499999999998</v>
+        <v>-61.20599999999996</v>
       </c>
       <c r="F47">
-        <v>357.2550000000001</v>
+        <v>365.1940000000001</v>
       </c>
       <c r="G47">
         <v>135.8</v>
@@ -5141,28 +5141,28 @@
         <v>111</v>
       </c>
       <c r="M47">
-        <v>19.7562015</v>
+        <v>20.19522820000001</v>
       </c>
       <c r="N47">
-        <v>91.24379849999998</v>
+        <v>90.80477179999998</v>
       </c>
       <c r="O47">
-        <v>21.89851164</v>
+        <v>21.79314523199999</v>
       </c>
       <c r="P47">
-        <v>69.34528685999999</v>
+        <v>69.011626568</v>
       </c>
       <c r="Q47">
-        <v>181.84528686</v>
+        <v>181.511626568</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2558124433452265</v>
+        <v>0.2591260427668834</v>
       </c>
       <c r="T47">
-        <v>1.031869297672393</v>
+        <v>1.048150244903563</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.618488959023827</v>
+        <v>5.496347894697221</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1592609430941171</v>
+        <v>0.1589124423483596</v>
       </c>
       <c r="C48">
-        <v>686.2230820378528</v>
+        <v>681.1051088788768</v>
       </c>
       <c r="D48">
-        <v>915.6170820378529</v>
+        <v>918.4381088788768</v>
       </c>
       <c r="E48">
-        <v>-61.20599999999996</v>
+        <v>-53.267</v>
       </c>
       <c r="F48">
-        <v>365.1940000000001</v>
+        <v>373.133</v>
       </c>
       <c r="G48">
         <v>135.8</v>
@@ -5223,28 +5223,28 @@
         <v>111</v>
       </c>
       <c r="M48">
-        <v>20.19522820000001</v>
+        <v>20.6342549</v>
       </c>
       <c r="N48">
-        <v>90.80477179999998</v>
+        <v>90.36574509999998</v>
       </c>
       <c r="O48">
-        <v>21.79314523199999</v>
+        <v>21.687778824</v>
       </c>
       <c r="P48">
-        <v>69.011626568</v>
+        <v>68.67796627599999</v>
       </c>
       <c r="Q48">
-        <v>181.511626568</v>
+        <v>181.177966276</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2591260427668834</v>
+        <v>0.2625646836761501</v>
       </c>
       <c r="T48">
-        <v>1.048150244903563</v>
+        <v>1.065045567501947</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.496347894697221</v>
+        <v>5.379404322469622</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1589124423483596</v>
+        <v>0.1585639416026021</v>
       </c>
       <c r="C49">
-        <v>681.1051088788768</v>
+        <v>676.0045726761459</v>
       </c>
       <c r="D49">
-        <v>918.4381088788768</v>
+        <v>921.2765726761461</v>
       </c>
       <c r="E49">
-        <v>-53.267</v>
+        <v>-45.32799999999997</v>
       </c>
       <c r="F49">
-        <v>373.133</v>
+        <v>381.0720000000001</v>
       </c>
       <c r="G49">
         <v>135.8</v>
@@ -5305,28 +5305,28 @@
         <v>111</v>
       </c>
       <c r="M49">
-        <v>20.6342549</v>
+        <v>21.0732816</v>
       </c>
       <c r="N49">
-        <v>90.36574509999998</v>
+        <v>89.92671839999998</v>
       </c>
       <c r="O49">
-        <v>21.687778824</v>
+        <v>21.582412416</v>
       </c>
       <c r="P49">
-        <v>68.67796627599999</v>
+        <v>68.34430598399999</v>
       </c>
       <c r="Q49">
-        <v>181.177966276</v>
+        <v>180.844305984</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2625646836761501</v>
+        <v>0.266135580005004</v>
       </c>
       <c r="T49">
-        <v>1.065045567501947</v>
+        <v>1.08259071020027</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.379404322469622</v>
+        <v>5.267333399084838</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1585639416026021</v>
+        <v>0.1582154408568446</v>
       </c>
       <c r="C50">
-        <v>676.0045726761463</v>
+        <v>670.9216355993476</v>
       </c>
       <c r="D50">
-        <v>921.2765726761462</v>
+        <v>924.1326355993476</v>
       </c>
       <c r="E50">
-        <v>-45.32800000000003</v>
+        <v>-37.38900000000001</v>
       </c>
       <c r="F50">
-        <v>381.072</v>
+        <v>389.011</v>
       </c>
       <c r="G50">
         <v>135.8</v>
@@ -5387,28 +5387,28 @@
         <v>111</v>
       </c>
       <c r="M50">
-        <v>21.0732816</v>
+        <v>21.5123083</v>
       </c>
       <c r="N50">
-        <v>89.92671839999998</v>
+        <v>89.48769169999998</v>
       </c>
       <c r="O50">
-        <v>21.582412416</v>
+        <v>21.47704600799999</v>
       </c>
       <c r="P50">
-        <v>68.34430598399999</v>
+        <v>68.010645692</v>
       </c>
       <c r="Q50">
-        <v>180.844305984</v>
+        <v>180.510645692</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.266135580005004</v>
+        <v>0.2698465114840089</v>
       </c>
       <c r="T50">
-        <v>1.08259071020027</v>
+        <v>1.100823897710291</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.267333399084838</v>
+        <v>5.159836799103515</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1582154408568446</v>
+        <v>0.157866940111087</v>
       </c>
       <c r="C51">
-        <v>670.9216355993476</v>
+        <v>665.8564618353987</v>
       </c>
       <c r="D51">
-        <v>924.1326355993476</v>
+        <v>927.0064618353988</v>
       </c>
       <c r="E51">
-        <v>-37.38900000000001</v>
+        <v>-29.44999999999999</v>
       </c>
       <c r="F51">
-        <v>389.011</v>
+        <v>396.95</v>
       </c>
       <c r="G51">
         <v>135.8</v>
@@ -5469,28 +5469,28 @@
         <v>111</v>
       </c>
       <c r="M51">
-        <v>21.5123083</v>
+        <v>21.951335</v>
       </c>
       <c r="N51">
-        <v>89.48769169999998</v>
+        <v>89.04866499999999</v>
       </c>
       <c r="O51">
-        <v>21.47704600799999</v>
+        <v>21.3716796</v>
       </c>
       <c r="P51">
-        <v>68.010645692</v>
+        <v>67.67698539999999</v>
       </c>
       <c r="Q51">
-        <v>180.510645692</v>
+        <v>180.1769854</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2698465114840089</v>
+        <v>0.2737058802221741</v>
       </c>
       <c r="T51">
-        <v>1.100823897710291</v>
+        <v>1.119786412720713</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.159836799103515</v>
+        <v>5.056640063121445</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.157866940111087</v>
+        <v>0.1575184393653295</v>
       </c>
       <c r="C52">
-        <v>665.8564618353987</v>
+        <v>660.8092176199136</v>
       </c>
       <c r="D52">
-        <v>927.0064618353988</v>
+        <v>929.8982176199138</v>
       </c>
       <c r="E52">
-        <v>-29.44999999999999</v>
+        <v>-21.51099999999997</v>
       </c>
       <c r="F52">
-        <v>396.95</v>
+        <v>404.8890000000001</v>
       </c>
       <c r="G52">
         <v>135.8</v>
@@ -5551,28 +5551,28 @@
         <v>111</v>
       </c>
       <c r="M52">
-        <v>21.951335</v>
+        <v>22.3903617</v>
       </c>
       <c r="N52">
-        <v>89.04866499999999</v>
+        <v>88.60963829999999</v>
       </c>
       <c r="O52">
-        <v>21.3716796</v>
+        <v>21.26631319199999</v>
       </c>
       <c r="P52">
-        <v>67.67698539999999</v>
+        <v>67.34332510799999</v>
       </c>
       <c r="Q52">
-        <v>180.1769854</v>
+        <v>179.843325108</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2737058802221741</v>
+        <v>0.2777227742149582</v>
       </c>
       <c r="T52">
-        <v>1.119786412720713</v>
+        <v>1.139522907935642</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.056640063121445</v>
+        <v>4.957490257962201</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1575184393653295</v>
+        <v>0.157169938619572</v>
       </c>
       <c r="C53">
-        <v>660.8092176199136</v>
+        <v>655.7800712692555</v>
       </c>
       <c r="D53">
-        <v>929.8982176199138</v>
+        <v>932.8080712692555</v>
       </c>
       <c r="E53">
-        <v>-21.51099999999997</v>
+        <v>-13.57199999999995</v>
       </c>
       <c r="F53">
-        <v>404.8890000000001</v>
+        <v>412.8280000000001</v>
       </c>
       <c r="G53">
         <v>135.8</v>
@@ -5633,28 +5633,28 @@
         <v>111</v>
       </c>
       <c r="M53">
-        <v>22.3903617</v>
+        <v>22.82938840000001</v>
       </c>
       <c r="N53">
-        <v>88.60963829999999</v>
+        <v>88.17061159999997</v>
       </c>
       <c r="O53">
-        <v>21.26631319199999</v>
+        <v>21.16094678399999</v>
       </c>
       <c r="P53">
-        <v>67.34332510799999</v>
+        <v>67.00966481599998</v>
       </c>
       <c r="Q53">
-        <v>179.843325108</v>
+        <v>179.509664816</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2777227742149582</v>
+        <v>0.2819070387907751</v>
       </c>
       <c r="T53">
-        <v>1.139522907935642</v>
+        <v>1.16008175711786</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.957490257962201</v>
+        <v>4.862153906847542</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.157169938619572</v>
+        <v>0.1568214378738145</v>
       </c>
       <c r="C54">
-        <v>655.7800712692555</v>
+        <v>650.7691932131941</v>
       </c>
       <c r="D54">
-        <v>932.8080712692555</v>
+        <v>935.7361932131942</v>
       </c>
       <c r="E54">
-        <v>-13.57199999999995</v>
+        <v>-5.632999999999981</v>
       </c>
       <c r="F54">
-        <v>412.8280000000001</v>
+        <v>420.7670000000001</v>
       </c>
       <c r="G54">
         <v>135.8</v>
@@ -5715,28 +5715,28 @@
         <v>111</v>
       </c>
       <c r="M54">
-        <v>22.82938840000001</v>
+        <v>23.2684151</v>
       </c>
       <c r="N54">
-        <v>88.17061159999997</v>
+        <v>87.73158489999999</v>
       </c>
       <c r="O54">
-        <v>21.16094678399999</v>
+        <v>21.05558037599999</v>
       </c>
       <c r="P54">
-        <v>67.00966481599998</v>
+        <v>66.67600452399999</v>
       </c>
       <c r="Q54">
-        <v>179.509664816</v>
+        <v>179.176004524</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2819070387907751</v>
+        <v>0.2862693571783287</v>
       </c>
       <c r="T54">
-        <v>1.16008175711786</v>
+        <v>1.18151545094613</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.862153906847542</v>
+        <v>4.770415153888155</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1568214378738145</v>
+        <v>0.156472937128057</v>
       </c>
       <c r="C55">
-        <v>650.7691932131941</v>
+        <v>645.7767560281827</v>
       </c>
       <c r="D55">
-        <v>935.7361932131942</v>
+        <v>938.6827560281829</v>
       </c>
       <c r="E55">
-        <v>-5.632999999999981</v>
+        <v>2.30600000000004</v>
       </c>
       <c r="F55">
-        <v>420.7670000000001</v>
+        <v>428.7060000000001</v>
       </c>
       <c r="G55">
         <v>135.8</v>
@@ -5797,28 +5797,28 @@
         <v>111</v>
       </c>
       <c r="M55">
-        <v>23.2684151</v>
+        <v>23.70744180000001</v>
       </c>
       <c r="N55">
-        <v>87.73158489999999</v>
+        <v>87.29255819999997</v>
       </c>
       <c r="O55">
-        <v>21.05558037599999</v>
+        <v>20.95021396799999</v>
       </c>
       <c r="P55">
-        <v>66.67600452399999</v>
+        <v>66.34234423199999</v>
       </c>
       <c r="Q55">
-        <v>179.176004524</v>
+        <v>178.842344232</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2862693571783287</v>
+        <v>0.2908213415827326</v>
       </c>
       <c r="T55">
-        <v>1.18151545094613</v>
+        <v>1.203881044506063</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.770415153888155</v>
+        <v>4.682074132519855</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.156472937128057</v>
+        <v>0.1561244363822995</v>
       </c>
       <c r="C56">
-        <v>645.7767560281827</v>
+        <v>640.8029344712608</v>
       </c>
       <c r="D56">
-        <v>938.6827560281829</v>
+        <v>941.6479344712609</v>
       </c>
       <c r="E56">
-        <v>2.30600000000004</v>
+        <v>10.24500000000006</v>
       </c>
       <c r="F56">
-        <v>428.7060000000001</v>
+        <v>436.6450000000001</v>
       </c>
       <c r="G56">
         <v>135.8</v>
@@ -5879,28 +5879,28 @@
         <v>111</v>
       </c>
       <c r="M56">
-        <v>23.70744180000001</v>
+        <v>24.1464685</v>
       </c>
       <c r="N56">
-        <v>87.29255819999997</v>
+        <v>86.85353149999997</v>
       </c>
       <c r="O56">
-        <v>20.95021396799999</v>
+        <v>20.84484755999999</v>
       </c>
       <c r="P56">
-        <v>66.34234423199999</v>
+        <v>66.00868393999998</v>
       </c>
       <c r="Q56">
-        <v>178.842344232</v>
+        <v>178.50868394</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2908213415827326</v>
+        <v>0.29557563640511</v>
       </c>
       <c r="T56">
-        <v>1.203881044506063</v>
+        <v>1.227240664446438</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.682074132519855</v>
+        <v>4.596945511928585</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1561244363822995</v>
+        <v>0.155775935636542</v>
       </c>
       <c r="C57">
-        <v>640.8029344712608</v>
+        <v>635.8479055146063</v>
       </c>
       <c r="D57">
-        <v>941.6479344712609</v>
+        <v>944.6319055146063</v>
       </c>
       <c r="E57">
-        <v>10.24500000000006</v>
+        <v>18.18400000000008</v>
       </c>
       <c r="F57">
-        <v>436.6450000000001</v>
+        <v>444.5840000000001</v>
       </c>
       <c r="G57">
         <v>135.8</v>
@@ -5961,28 +5961,28 @@
         <v>111</v>
       </c>
       <c r="M57">
-        <v>24.1464685</v>
+        <v>24.58549520000001</v>
       </c>
       <c r="N57">
-        <v>86.85353149999997</v>
+        <v>86.41450479999997</v>
       </c>
       <c r="O57">
-        <v>20.84484755999999</v>
+        <v>20.73948115199999</v>
       </c>
       <c r="P57">
-        <v>66.00868393999998</v>
+        <v>65.67502364799998</v>
       </c>
       <c r="Q57">
-        <v>178.50868394</v>
+        <v>178.175023648</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.29557563640511</v>
+        <v>0.3005460355375954</v>
       </c>
       <c r="T57">
-        <v>1.227240664446438</v>
+        <v>1.251662085293194</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.596945511928585</v>
+        <v>4.514857199215575</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.155775935636542</v>
+        <v>0.1565104348907845</v>
       </c>
       <c r="C58">
-        <v>635.8479055146063</v>
+        <v>621.6418230050069</v>
       </c>
       <c r="D58">
-        <v>944.6319055146063</v>
+        <v>938.3648230050071</v>
       </c>
       <c r="E58">
-        <v>18.18400000000008</v>
+        <v>26.12300000000005</v>
       </c>
       <c r="F58">
-        <v>444.5840000000001</v>
+        <v>452.5230000000001</v>
       </c>
       <c r="G58">
         <v>135.8</v>
@@ -6043,45 +6043,45 @@
         <v>111</v>
       </c>
       <c r="M58">
-        <v>24.58549520000001</v>
+        <v>26.15582940000001</v>
       </c>
       <c r="N58">
-        <v>86.41450479999997</v>
+        <v>84.84417059999998</v>
       </c>
       <c r="O58">
-        <v>20.73948115199999</v>
+        <v>20.362600944</v>
       </c>
       <c r="P58">
-        <v>65.67502364799998</v>
+        <v>64.48156965599999</v>
       </c>
       <c r="Q58">
-        <v>178.175023648</v>
+        <v>176.981569656</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3005460355375954</v>
+        <v>0.3057476160250802</v>
       </c>
       <c r="T58">
-        <v>1.251662085293194</v>
+        <v>1.277219386179334</v>
       </c>
       <c r="U58">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V58">
         <v>0.24</v>
       </c>
       <c r="W58">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>4.514857199215575</v>
+        <v>4.243795840020273</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1565104348907845</v>
+        <v>0.156180934145027</v>
       </c>
       <c r="C59">
-        <v>621.6418230050069</v>
+        <v>616.5039581047203</v>
       </c>
       <c r="D59">
-        <v>938.3648230050071</v>
+        <v>941.1659581047204</v>
       </c>
       <c r="E59">
-        <v>26.12300000000005</v>
+        <v>34.06200000000007</v>
       </c>
       <c r="F59">
-        <v>452.5230000000001</v>
+        <v>460.4620000000001</v>
       </c>
       <c r="G59">
         <v>135.8</v>
@@ -6125,28 +6125,28 @@
         <v>111</v>
       </c>
       <c r="M59">
-        <v>26.15582940000001</v>
+        <v>26.61470360000001</v>
       </c>
       <c r="N59">
-        <v>84.84417059999998</v>
+        <v>84.38529639999997</v>
       </c>
       <c r="O59">
-        <v>20.362600944</v>
+        <v>20.25247113599999</v>
       </c>
       <c r="P59">
-        <v>64.48156965599999</v>
+        <v>64.13282526399998</v>
       </c>
       <c r="Q59">
-        <v>176.981569656</v>
+        <v>176.632825264</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3057476160250802</v>
+        <v>0.3111968908214928</v>
       </c>
       <c r="T59">
-        <v>1.277219386179334</v>
+        <v>1.303993701393384</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.243795840020273</v>
+        <v>4.17062694622682</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.156180934145027</v>
+        <v>0.1558514333992695</v>
       </c>
       <c r="C60">
-        <v>616.5039581047201</v>
+        <v>611.3828667452374</v>
       </c>
       <c r="D60">
-        <v>941.1659581047202</v>
+        <v>943.9838667452374</v>
       </c>
       <c r="E60">
-        <v>34.06200000000001</v>
+        <v>42.00099999999998</v>
       </c>
       <c r="F60">
-        <v>460.462</v>
+        <v>468.401</v>
       </c>
       <c r="G60">
         <v>135.8</v>
@@ -6207,28 +6207,28 @@
         <v>111</v>
       </c>
       <c r="M60">
-        <v>26.61470360000001</v>
+        <v>27.0735778</v>
       </c>
       <c r="N60">
-        <v>84.38529639999999</v>
+        <v>83.92642219999999</v>
       </c>
       <c r="O60">
-        <v>20.252471136</v>
+        <v>20.142341328</v>
       </c>
       <c r="P60">
-        <v>64.13282526399999</v>
+        <v>63.78408087199999</v>
       </c>
       <c r="Q60">
-        <v>176.632825264</v>
+        <v>176.284080872</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3111968908214928</v>
+        <v>0.3169119839006572</v>
       </c>
       <c r="T60">
-        <v>1.303993701393384</v>
+        <v>1.332074080764219</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.170626946226821</v>
+        <v>4.099938353917892</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1558514333992695</v>
+        <v>0.1555219326535119</v>
       </c>
       <c r="C61">
-        <v>611.3828667452374</v>
+        <v>606.2787000420391</v>
       </c>
       <c r="D61">
-        <v>943.9838667452374</v>
+        <v>946.8187000420392</v>
       </c>
       <c r="E61">
-        <v>42.00099999999998</v>
+        <v>49.94</v>
       </c>
       <c r="F61">
-        <v>468.401</v>
+        <v>476.34</v>
       </c>
       <c r="G61">
         <v>135.8</v>
@@ -6289,28 +6289,28 @@
         <v>111</v>
       </c>
       <c r="M61">
-        <v>27.0735778</v>
+        <v>27.532452</v>
       </c>
       <c r="N61">
-        <v>83.92642219999999</v>
+        <v>83.46754799999998</v>
       </c>
       <c r="O61">
-        <v>20.142341328</v>
+        <v>20.03221151999999</v>
       </c>
       <c r="P61">
-        <v>63.78408087199999</v>
+        <v>63.43533647999999</v>
       </c>
       <c r="Q61">
-        <v>176.284080872</v>
+        <v>175.93533648</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3169119839006572</v>
+        <v>0.3229128316337798</v>
       </c>
       <c r="T61">
-        <v>1.332074080764219</v>
+        <v>1.361558479103594</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.099938353917892</v>
+        <v>4.03160604801926</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1555219326535119</v>
+        <v>0.1568150319077544</v>
       </c>
       <c r="C62">
-        <v>606.2787000420391</v>
+        <v>587.3111885523108</v>
       </c>
       <c r="D62">
-        <v>946.8187000420392</v>
+        <v>935.7901885523108</v>
       </c>
       <c r="E62">
-        <v>49.94</v>
+        <v>57.87900000000002</v>
       </c>
       <c r="F62">
-        <v>476.34</v>
+        <v>484.2790000000001</v>
       </c>
       <c r="G62">
         <v>135.8</v>
@@ -6371,45 +6371,45 @@
         <v>111</v>
       </c>
       <c r="M62">
-        <v>27.532452</v>
+        <v>29.6863027</v>
       </c>
       <c r="N62">
-        <v>83.46754799999998</v>
+        <v>81.31369729999999</v>
       </c>
       <c r="O62">
-        <v>20.03221151999999</v>
+        <v>19.515287352</v>
       </c>
       <c r="P62">
-        <v>63.43533647999999</v>
+        <v>61.79840994799999</v>
       </c>
       <c r="Q62">
-        <v>175.93533648</v>
+        <v>174.298409948</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3229128316337798</v>
+        <v>0.3292214151480883</v>
       </c>
       <c r="T62">
-        <v>1.361558479103594</v>
+        <v>1.39255489787063</v>
       </c>
       <c r="U62">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V62">
         <v>0.24</v>
       </c>
       <c r="W62">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>4.03160604801926</v>
+        <v>3.739098166643702</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1568150319077544</v>
+        <v>0.1565121311619969</v>
       </c>
       <c r="C63">
-        <v>587.3111885523108</v>
+        <v>581.9324458882506</v>
       </c>
       <c r="D63">
-        <v>935.7901885523108</v>
+        <v>938.3504458882508</v>
       </c>
       <c r="E63">
-        <v>57.87900000000002</v>
+        <v>65.81800000000004</v>
       </c>
       <c r="F63">
-        <v>484.2790000000001</v>
+        <v>492.2180000000001</v>
       </c>
       <c r="G63">
         <v>135.8</v>
@@ -6453,28 +6453,28 @@
         <v>111</v>
       </c>
       <c r="M63">
-        <v>29.6863027</v>
+        <v>30.1729634</v>
       </c>
       <c r="N63">
-        <v>81.31369729999999</v>
+        <v>80.82703659999999</v>
       </c>
       <c r="O63">
-        <v>19.515287352</v>
+        <v>19.39848878399999</v>
       </c>
       <c r="P63">
-        <v>61.79840994799999</v>
+        <v>61.42854781599999</v>
       </c>
       <c r="Q63">
-        <v>174.298409948</v>
+        <v>173.928547816</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3292214151480883</v>
+        <v>0.3358620293736762</v>
       </c>
       <c r="T63">
-        <v>1.39255489787063</v>
+        <v>1.42518270709909</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.739098166643702</v>
+        <v>3.678790131697836</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1565121311619969</v>
+        <v>0.1562092304162394</v>
       </c>
       <c r="C64">
-        <v>581.9324458882506</v>
+        <v>576.5677510325758</v>
       </c>
       <c r="D64">
-        <v>938.3504458882508</v>
+        <v>940.9247510325757</v>
       </c>
       <c r="E64">
-        <v>65.81800000000004</v>
+        <v>73.75700000000001</v>
       </c>
       <c r="F64">
-        <v>492.2180000000001</v>
+        <v>500.157</v>
       </c>
       <c r="G64">
         <v>135.8</v>
@@ -6535,28 +6535,28 @@
         <v>111</v>
       </c>
       <c r="M64">
-        <v>30.1729634</v>
+        <v>30.6596241</v>
       </c>
       <c r="N64">
-        <v>80.82703659999999</v>
+        <v>80.34037589999998</v>
       </c>
       <c r="O64">
-        <v>19.39848878399999</v>
+        <v>19.28169021599999</v>
       </c>
       <c r="P64">
-        <v>61.42854781599999</v>
+        <v>61.05868568399999</v>
       </c>
       <c r="Q64">
-        <v>173.928547816</v>
+        <v>173.558685684</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3358620293736762</v>
+        <v>0.3428615957195659</v>
       </c>
       <c r="T64">
-        <v>1.42518270709909</v>
+        <v>1.459574181691249</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.678790131697836</v>
+        <v>3.620396637543902</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1562092304162394</v>
+        <v>0.1559063296704819</v>
       </c>
       <c r="C65">
-        <v>576.5677510325758</v>
+        <v>571.2172199211709</v>
       </c>
       <c r="D65">
-        <v>940.9247510325757</v>
+        <v>943.513219921171</v>
       </c>
       <c r="E65">
-        <v>73.75700000000001</v>
+        <v>81.69600000000003</v>
       </c>
       <c r="F65">
-        <v>500.157</v>
+        <v>508.0960000000001</v>
       </c>
       <c r="G65">
         <v>135.8</v>
@@ -6617,28 +6617,28 @@
         <v>111</v>
       </c>
       <c r="M65">
-        <v>30.6596241</v>
+        <v>31.1462848</v>
       </c>
       <c r="N65">
-        <v>80.34037589999998</v>
+        <v>79.85371519999998</v>
       </c>
       <c r="O65">
-        <v>19.28169021599999</v>
+        <v>19.16489164799999</v>
       </c>
       <c r="P65">
-        <v>61.05868568399999</v>
+        <v>60.68882355199999</v>
       </c>
       <c r="Q65">
-        <v>173.558685684</v>
+        <v>173.188823552</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3428615957195659</v>
+        <v>0.3502500268624497</v>
       </c>
       <c r="T65">
-        <v>1.459574181691249</v>
+        <v>1.495876293760751</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.620396637543902</v>
+        <v>3.563827940082278</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1559063296704819</v>
+        <v>0.1556034289247244</v>
       </c>
       <c r="C66">
-        <v>571.2172199211709</v>
+        <v>565.8809697691934</v>
       </c>
       <c r="D66">
-        <v>943.513219921171</v>
+        <v>946.1159697691935</v>
       </c>
       <c r="E66">
-        <v>81.69600000000003</v>
+        <v>89.63500000000005</v>
       </c>
       <c r="F66">
-        <v>508.0960000000001</v>
+        <v>516.0350000000001</v>
       </c>
       <c r="G66">
         <v>135.8</v>
@@ -6699,28 +6699,28 @@
         <v>111</v>
       </c>
       <c r="M66">
-        <v>31.1462848</v>
+        <v>31.63294550000001</v>
       </c>
       <c r="N66">
-        <v>79.85371519999998</v>
+        <v>79.36705449999998</v>
       </c>
       <c r="O66">
-        <v>19.16489164799999</v>
+        <v>19.04809307999999</v>
       </c>
       <c r="P66">
-        <v>60.68882355199999</v>
+        <v>60.31896141999999</v>
       </c>
       <c r="Q66">
-        <v>173.188823552</v>
+        <v>172.81896142</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3502500268624497</v>
+        <v>0.3580606540706411</v>
       </c>
       <c r="T66">
-        <v>1.495876293760751</v>
+        <v>1.534252812234224</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.563827940082278</v>
+        <v>3.508999817927166</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1556034289247244</v>
+        <v>0.1567050081789669</v>
       </c>
       <c r="C67">
-        <v>565.8809697691934</v>
+        <v>548.5445427141102</v>
       </c>
       <c r="D67">
-        <v>946.1159697691935</v>
+        <v>936.7185427141103</v>
       </c>
       <c r="E67">
-        <v>89.63500000000005</v>
+        <v>97.57400000000001</v>
       </c>
       <c r="F67">
-        <v>516.0350000000001</v>
+        <v>523.974</v>
       </c>
       <c r="G67">
         <v>135.8</v>
@@ -6781,45 +6781,45 @@
         <v>111</v>
       </c>
       <c r="M67">
-        <v>31.63294550000001</v>
+        <v>33.58673340000001</v>
       </c>
       <c r="N67">
-        <v>79.36705449999998</v>
+        <v>77.41326659999999</v>
       </c>
       <c r="O67">
-        <v>19.04809307999999</v>
+        <v>18.579183984</v>
       </c>
       <c r="P67">
-        <v>60.31896141999999</v>
+        <v>58.83408261599999</v>
       </c>
       <c r="Q67">
-        <v>172.81896142</v>
+        <v>171.334082616</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3580606540706411</v>
+        <v>0.3663307299381379</v>
       </c>
       <c r="T67">
-        <v>1.534252812234224</v>
+        <v>1.574886772970843</v>
       </c>
       <c r="U67">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V67">
         <v>0.24</v>
       </c>
       <c r="W67">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>3.508999817927166</v>
+        <v>3.304876323578403</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1567050081789669</v>
+        <v>0.1564233874332094</v>
       </c>
       <c r="C68">
-        <v>548.5445427141102</v>
+        <v>542.9902045897312</v>
       </c>
       <c r="D68">
-        <v>936.7185427141103</v>
+        <v>939.1032045897314</v>
       </c>
       <c r="E68">
-        <v>97.57400000000001</v>
+        <v>105.5130000000001</v>
       </c>
       <c r="F68">
-        <v>523.974</v>
+        <v>531.9130000000001</v>
       </c>
       <c r="G68">
         <v>135.8</v>
@@ -6863,28 +6863,28 @@
         <v>111</v>
       </c>
       <c r="M68">
-        <v>33.58673340000001</v>
+        <v>34.09562330000001</v>
       </c>
       <c r="N68">
-        <v>77.41326659999999</v>
+        <v>76.90437669999997</v>
       </c>
       <c r="O68">
-        <v>18.579183984</v>
+        <v>18.45705040799999</v>
       </c>
       <c r="P68">
-        <v>58.83408261599999</v>
+        <v>58.44732629199998</v>
       </c>
       <c r="Q68">
-        <v>171.334082616</v>
+        <v>170.947326292</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3663307299381379</v>
+        <v>0.375102022524877</v>
       </c>
       <c r="T68">
-        <v>1.574886772970843</v>
+        <v>1.617983397994529</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.304876323578403</v>
+        <v>3.255549811286188</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1564233874332094</v>
+        <v>0.1561417666874519</v>
       </c>
       <c r="C69">
-        <v>542.9902045897312</v>
+        <v>537.4480390138976</v>
       </c>
       <c r="D69">
-        <v>939.1032045897314</v>
+        <v>941.5000390138978</v>
       </c>
       <c r="E69">
-        <v>105.5130000000001</v>
+        <v>113.4520000000001</v>
       </c>
       <c r="F69">
-        <v>531.9130000000001</v>
+        <v>539.8520000000001</v>
       </c>
       <c r="G69">
         <v>135.8</v>
@@ -6945,28 +6945,28 @@
         <v>111</v>
       </c>
       <c r="M69">
-        <v>34.09562330000001</v>
+        <v>34.60451320000001</v>
       </c>
       <c r="N69">
-        <v>76.90437669999997</v>
+        <v>76.39548679999999</v>
       </c>
       <c r="O69">
-        <v>18.45705040799999</v>
+        <v>18.334916832</v>
       </c>
       <c r="P69">
-        <v>58.44732629199998</v>
+        <v>58.06056996799999</v>
       </c>
       <c r="Q69">
-        <v>170.947326292</v>
+        <v>170.560569968</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.375102022524877</v>
+        <v>0.3844215208982871</v>
       </c>
       <c r="T69">
-        <v>1.617983397994529</v>
+        <v>1.663773562082196</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.255549811286188</v>
+        <v>3.207674078767274</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1561417666874519</v>
+        <v>0.1558601459416944</v>
       </c>
       <c r="C70">
-        <v>537.4480390138976</v>
+        <v>531.9181394275776</v>
       </c>
       <c r="D70">
-        <v>941.5000390138978</v>
+        <v>943.9091394275777</v>
       </c>
       <c r="E70">
-        <v>113.4520000000001</v>
+        <v>121.391</v>
       </c>
       <c r="F70">
-        <v>539.8520000000001</v>
+        <v>547.7910000000001</v>
       </c>
       <c r="G70">
         <v>135.8</v>
@@ -7027,28 +7027,28 @@
         <v>111</v>
       </c>
       <c r="M70">
-        <v>34.60451320000001</v>
+        <v>35.11340310000001</v>
       </c>
       <c r="N70">
-        <v>76.39548679999999</v>
+        <v>75.88659689999997</v>
       </c>
       <c r="O70">
-        <v>18.334916832</v>
+        <v>18.21278325599999</v>
       </c>
       <c r="P70">
-        <v>58.06056996799999</v>
+        <v>57.67381364399998</v>
       </c>
       <c r="Q70">
-        <v>170.560569968</v>
+        <v>170.173813644</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3844215208982871</v>
+        <v>0.3943422772312722</v>
       </c>
       <c r="T70">
-        <v>1.663773562082196</v>
+        <v>1.712517930304551</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.207674078767274</v>
+        <v>3.161186048640212</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1558601459416944</v>
+        <v>0.1555785251959368</v>
       </c>
       <c r="C71">
-        <v>531.9181394275776</v>
+        <v>526.4006002305763</v>
       </c>
       <c r="D71">
-        <v>943.9091394275777</v>
+        <v>946.3306002305765</v>
       </c>
       <c r="E71">
-        <v>121.391</v>
+        <v>129.3300000000001</v>
       </c>
       <c r="F71">
-        <v>547.7910000000001</v>
+        <v>555.7300000000001</v>
       </c>
       <c r="G71">
         <v>135.8</v>
@@ -7109,28 +7109,28 @@
         <v>111</v>
       </c>
       <c r="M71">
-        <v>35.11340310000001</v>
+        <v>35.62229300000001</v>
       </c>
       <c r="N71">
-        <v>75.88659689999997</v>
+        <v>75.37770699999997</v>
       </c>
       <c r="O71">
-        <v>18.21278325599999</v>
+        <v>18.09064967999999</v>
       </c>
       <c r="P71">
-        <v>57.67381364399998</v>
+        <v>57.28705731999998</v>
       </c>
       <c r="Q71">
-        <v>170.173813644</v>
+        <v>169.78705732</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3943422772312722</v>
+        <v>0.4049244173197895</v>
       </c>
       <c r="T71">
-        <v>1.712517930304551</v>
+        <v>1.764511923075063</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.161186048640212</v>
+        <v>3.116026247945351</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1555785251959368</v>
+        <v>0.1552969044501793</v>
       </c>
       <c r="C72">
-        <v>526.4006002305763</v>
+        <v>520.8955167938643</v>
       </c>
       <c r="D72">
-        <v>946.3306002305765</v>
+        <v>948.7645167938645</v>
       </c>
       <c r="E72">
-        <v>129.3300000000001</v>
+        <v>137.2690000000001</v>
       </c>
       <c r="F72">
-        <v>555.7300000000001</v>
+        <v>563.6690000000001</v>
       </c>
       <c r="G72">
         <v>135.8</v>
@@ -7191,28 +7191,28 @@
         <v>111</v>
       </c>
       <c r="M72">
-        <v>35.62229300000001</v>
+        <v>36.13118290000001</v>
       </c>
       <c r="N72">
-        <v>75.37770699999997</v>
+        <v>74.86881709999997</v>
       </c>
       <c r="O72">
-        <v>18.09064967999999</v>
+        <v>17.96851610399999</v>
       </c>
       <c r="P72">
-        <v>57.28705731999998</v>
+        <v>56.90030099599998</v>
       </c>
       <c r="Q72">
-        <v>169.78705732</v>
+        <v>169.400300996</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4049244173197895</v>
+        <v>0.4162363601730323</v>
       </c>
       <c r="T72">
-        <v>1.764511923075063</v>
+        <v>1.820091708450439</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.116026247945351</v>
+        <v>3.072138554312319</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1552969044501794</v>
+        <v>0.1550152837044218</v>
       </c>
       <c r="C73">
-        <v>520.8955167938642</v>
+        <v>515.4029854721026</v>
       </c>
       <c r="D73">
-        <v>948.7645167938642</v>
+        <v>951.2109854721027</v>
       </c>
       <c r="E73">
-        <v>137.2689999999999</v>
+        <v>145.208</v>
       </c>
       <c r="F73">
-        <v>563.669</v>
+        <v>571.6080000000001</v>
       </c>
       <c r="G73">
         <v>135.8</v>
@@ -7273,28 +7273,28 @@
         <v>111</v>
       </c>
       <c r="M73">
-        <v>36.1311829</v>
+        <v>36.64007280000001</v>
       </c>
       <c r="N73">
-        <v>74.86881709999999</v>
+        <v>74.35992719999999</v>
       </c>
       <c r="O73">
-        <v>17.968516104</v>
+        <v>17.846382528</v>
       </c>
       <c r="P73">
-        <v>56.90030099599999</v>
+        <v>56.51354467199999</v>
       </c>
       <c r="Q73">
-        <v>169.400300996</v>
+        <v>169.013544672</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4162363601730322</v>
+        <v>0.4283562989443636</v>
       </c>
       <c r="T73">
-        <v>1.820091708450438</v>
+        <v>1.879641478495483</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.072138554312319</v>
+        <v>3.029469963280203</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1550152837044218</v>
+        <v>0.1590611029586643</v>
       </c>
       <c r="C74">
-        <v>515.4029854721026</v>
+        <v>473.4856149694372</v>
       </c>
       <c r="D74">
-        <v>951.2109854721027</v>
+        <v>917.2326149694372</v>
       </c>
       <c r="E74">
-        <v>145.208</v>
+        <v>153.147</v>
       </c>
       <c r="F74">
-        <v>571.6080000000001</v>
+        <v>579.547</v>
       </c>
       <c r="G74">
         <v>135.8</v>
@@ -7355,45 +7355,45 @@
         <v>111</v>
       </c>
       <c r="M74">
-        <v>36.64007280000001</v>
+        <v>41.6694293</v>
       </c>
       <c r="N74">
-        <v>74.35992719999999</v>
+        <v>69.33057069999998</v>
       </c>
       <c r="O74">
-        <v>17.846382528</v>
+        <v>16.63933696799999</v>
       </c>
       <c r="P74">
-        <v>56.51354467199999</v>
+        <v>52.69123373199999</v>
       </c>
       <c r="Q74">
-        <v>169.013544672</v>
+        <v>165.191233732</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4283562989443636</v>
+        <v>0.4413740109580159</v>
       </c>
       <c r="T74">
-        <v>1.879641478495483</v>
+        <v>1.943602342617938</v>
       </c>
       <c r="U74">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V74">
         <v>0.24</v>
       </c>
       <c r="W74">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>3.029469963280203</v>
+        <v>2.663823379985671</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1590611029586643</v>
+        <v>0.1588387622129068</v>
       </c>
       <c r="C75">
-        <v>473.4856149694372</v>
+        <v>467.3507587839397</v>
       </c>
       <c r="D75">
-        <v>917.2326149694372</v>
+        <v>919.0367587839397</v>
       </c>
       <c r="E75">
-        <v>153.147</v>
+        <v>161.0860000000001</v>
       </c>
       <c r="F75">
-        <v>579.547</v>
+        <v>587.4860000000001</v>
       </c>
       <c r="G75">
         <v>135.8</v>
@@ -7437,28 +7437,28 @@
         <v>111</v>
       </c>
       <c r="M75">
-        <v>41.6694293</v>
+        <v>42.24024340000001</v>
       </c>
       <c r="N75">
-        <v>69.33057069999998</v>
+        <v>68.75975659999997</v>
       </c>
       <c r="O75">
-        <v>16.63933696799999</v>
+        <v>16.50234158399999</v>
       </c>
       <c r="P75">
-        <v>52.69123373199999</v>
+        <v>52.25741501599998</v>
       </c>
       <c r="Q75">
-        <v>165.191233732</v>
+        <v>164.757415016</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4413740109580159</v>
+        <v>0.4553930854342569</v>
       </c>
       <c r="T75">
-        <v>1.943602342617938</v>
+        <v>2.012483273211351</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.663823379985671</v>
+        <v>2.627825766742621</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1588387622129068</v>
+        <v>0.1586164214671493</v>
       </c>
       <c r="C76">
-        <v>467.3507587839397</v>
+        <v>461.2230138802207</v>
       </c>
       <c r="D76">
-        <v>919.0367587839397</v>
+        <v>920.8480138802208</v>
       </c>
       <c r="E76">
-        <v>161.0860000000001</v>
+        <v>169.025</v>
       </c>
       <c r="F76">
-        <v>587.4860000000001</v>
+        <v>595.4250000000001</v>
       </c>
       <c r="G76">
         <v>135.8</v>
@@ -7519,28 +7519,28 @@
         <v>111</v>
       </c>
       <c r="M76">
-        <v>42.24024340000001</v>
+        <v>42.81105750000001</v>
       </c>
       <c r="N76">
-        <v>68.75975659999997</v>
+        <v>68.18894249999997</v>
       </c>
       <c r="O76">
-        <v>16.50234158399999</v>
+        <v>16.36534619999999</v>
       </c>
       <c r="P76">
-        <v>52.25741501599998</v>
+        <v>51.82359629999998</v>
       </c>
       <c r="Q76">
-        <v>164.757415016</v>
+        <v>164.3235963</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4553930854342569</v>
+        <v>0.4705336858685972</v>
       </c>
       <c r="T76">
-        <v>2.012483273211351</v>
+        <v>2.086874678252238</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.627825766742621</v>
+        <v>2.59278808985272</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1586164214671493</v>
+        <v>0.1583940807213918</v>
       </c>
       <c r="C77">
-        <v>461.2230138802207</v>
+        <v>455.1024223864556</v>
       </c>
       <c r="D77">
-        <v>920.8480138802208</v>
+        <v>922.6664223864556</v>
       </c>
       <c r="E77">
-        <v>169.025</v>
+        <v>176.964</v>
       </c>
       <c r="F77">
-        <v>595.4250000000001</v>
+        <v>603.364</v>
       </c>
       <c r="G77">
         <v>135.8</v>
@@ -7601,28 +7601,28 @@
         <v>111</v>
       </c>
       <c r="M77">
-        <v>42.81105750000001</v>
+        <v>43.3818716</v>
       </c>
       <c r="N77">
-        <v>68.18894249999997</v>
+        <v>67.61812839999999</v>
       </c>
       <c r="O77">
-        <v>16.36534619999999</v>
+        <v>16.228350816</v>
       </c>
       <c r="P77">
-        <v>51.82359629999998</v>
+        <v>51.38977758399999</v>
       </c>
       <c r="Q77">
-        <v>164.3235963</v>
+        <v>163.889777584</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4705336858685972</v>
+        <v>0.4869360030057991</v>
       </c>
       <c r="T77">
-        <v>2.086874678252238</v>
+        <v>2.167465367046532</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.59278808985272</v>
+        <v>2.5586724570915</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1583940807213918</v>
+        <v>0.1581717399756342</v>
       </c>
       <c r="C78">
-        <v>455.1024223864556</v>
+        <v>448.9890267642406</v>
       </c>
       <c r="D78">
-        <v>922.6664223864556</v>
+        <v>924.4920267642407</v>
       </c>
       <c r="E78">
-        <v>176.964</v>
+        <v>184.9030000000001</v>
       </c>
       <c r="F78">
-        <v>603.364</v>
+        <v>611.3030000000001</v>
       </c>
       <c r="G78">
         <v>135.8</v>
@@ -7683,28 +7683,28 @@
         <v>111</v>
       </c>
       <c r="M78">
-        <v>43.3818716</v>
+        <v>43.95268570000001</v>
       </c>
       <c r="N78">
-        <v>67.61812839999999</v>
+        <v>67.04731429999998</v>
       </c>
       <c r="O78">
-        <v>16.228350816</v>
+        <v>16.091355432</v>
       </c>
       <c r="P78">
-        <v>51.38977758399999</v>
+        <v>50.95595886799998</v>
       </c>
       <c r="Q78">
-        <v>163.889777584</v>
+        <v>163.455958868</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4869360030057991</v>
+        <v>0.5047646085897142</v>
       </c>
       <c r="T78">
-        <v>2.167465367046532</v>
+        <v>2.255063941822938</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.5586724570915</v>
+        <v>2.52544294466174</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1581717399756342</v>
+        <v>0.1602613192298768</v>
       </c>
       <c r="C79">
-        <v>448.9890267642406</v>
+        <v>424.172715085179</v>
       </c>
       <c r="D79">
-        <v>924.4920267642407</v>
+        <v>907.6147150851791</v>
       </c>
       <c r="E79">
-        <v>184.9030000000001</v>
+        <v>192.842</v>
       </c>
       <c r="F79">
-        <v>611.3030000000001</v>
+        <v>619.2420000000001</v>
       </c>
       <c r="G79">
         <v>135.8</v>
@@ -7765,45 +7765,45 @@
         <v>111</v>
       </c>
       <c r="M79">
-        <v>43.95268570000001</v>
+        <v>46.93854360000001</v>
       </c>
       <c r="N79">
-        <v>67.04731429999998</v>
+        <v>64.06145639999997</v>
       </c>
       <c r="O79">
-        <v>16.091355432</v>
+        <v>15.37474953599999</v>
       </c>
       <c r="P79">
-        <v>50.95595886799998</v>
+        <v>48.68670686399997</v>
       </c>
       <c r="Q79">
-        <v>163.455958868</v>
+        <v>161.186706864</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5047646085897142</v>
+        <v>0.5242139964994399</v>
       </c>
       <c r="T79">
-        <v>2.255063941822938</v>
+        <v>2.3506260233972</v>
       </c>
       <c r="U79">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V79">
         <v>0.24</v>
       </c>
       <c r="W79">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.52544294466174</v>
+        <v>2.36479429242453</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1602613192298768</v>
+        <v>0.1600686184841192</v>
       </c>
       <c r="C80">
-        <v>424.172715085179</v>
+        <v>417.7643018269949</v>
       </c>
       <c r="D80">
-        <v>907.6147150851791</v>
+        <v>909.145301826995</v>
       </c>
       <c r="E80">
-        <v>192.842</v>
+        <v>200.7810000000001</v>
       </c>
       <c r="F80">
-        <v>619.2420000000001</v>
+        <v>627.1810000000002</v>
       </c>
       <c r="G80">
         <v>135.8</v>
@@ -7847,28 +7847,28 @@
         <v>111</v>
       </c>
       <c r="M80">
-        <v>46.93854360000001</v>
+        <v>47.54031980000001</v>
       </c>
       <c r="N80">
-        <v>64.06145639999997</v>
+        <v>63.45968019999997</v>
       </c>
       <c r="O80">
-        <v>15.37474953599999</v>
+        <v>15.23032324799999</v>
       </c>
       <c r="P80">
-        <v>48.68670686399997</v>
+        <v>48.22935695199998</v>
       </c>
       <c r="Q80">
-        <v>161.186706864</v>
+        <v>160.729356952</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5242139964994399</v>
+        <v>0.5455157070672345</v>
       </c>
       <c r="T80">
-        <v>2.3506260233972</v>
+        <v>2.455289255597581</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.36479429242453</v>
+        <v>2.334860187457131</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1600686184841192</v>
+        <v>0.1598759177383617</v>
       </c>
       <c r="C81">
-        <v>417.7643018269949</v>
+        <v>411.3610596024951</v>
       </c>
       <c r="D81">
-        <v>909.145301826995</v>
+        <v>910.6810596024951</v>
       </c>
       <c r="E81">
-        <v>200.7810000000001</v>
+        <v>208.7200000000001</v>
       </c>
       <c r="F81">
-        <v>627.1810000000002</v>
+        <v>635.1200000000001</v>
       </c>
       <c r="G81">
         <v>135.8</v>
@@ -7929,28 +7929,28 @@
         <v>111</v>
       </c>
       <c r="M81">
-        <v>47.54031980000001</v>
+        <v>48.14209600000002</v>
       </c>
       <c r="N81">
-        <v>63.45968019999997</v>
+        <v>62.85790399999997</v>
       </c>
       <c r="O81">
-        <v>15.23032324799999</v>
+        <v>15.08589695999999</v>
       </c>
       <c r="P81">
-        <v>48.22935695199998</v>
+        <v>47.77200703999998</v>
       </c>
       <c r="Q81">
-        <v>160.729356952</v>
+        <v>160.27200704</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5455157070672345</v>
+        <v>0.5689475886918087</v>
       </c>
       <c r="T81">
-        <v>2.455289255597581</v>
+        <v>2.570418811018001</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.334860187457131</v>
+        <v>2.305674435113917</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1598759177383617</v>
+        <v>0.1596832169926042</v>
       </c>
       <c r="C82">
-        <v>411.3610596024951</v>
+        <v>404.9630146612552</v>
       </c>
       <c r="D82">
-        <v>910.6810596024951</v>
+        <v>912.2220146612553</v>
       </c>
       <c r="E82">
-        <v>208.7200000000001</v>
+        <v>216.659</v>
       </c>
       <c r="F82">
-        <v>635.1200000000001</v>
+        <v>643.0590000000001</v>
       </c>
       <c r="G82">
         <v>135.8</v>
@@ -8011,28 +8011,28 @@
         <v>111</v>
       </c>
       <c r="M82">
-        <v>48.14209600000002</v>
+        <v>48.74387220000001</v>
       </c>
       <c r="N82">
-        <v>62.85790399999997</v>
+        <v>62.25612779999997</v>
       </c>
       <c r="O82">
-        <v>15.08589695999999</v>
+        <v>14.94147067199999</v>
       </c>
       <c r="P82">
-        <v>47.77200703999998</v>
+        <v>47.31465712799998</v>
       </c>
       <c r="Q82">
-        <v>160.27200704</v>
+        <v>159.814657128</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5689475886918087</v>
+        <v>0.5948459841716013</v>
       </c>
       <c r="T82">
-        <v>2.570418811018001</v>
+        <v>2.697667267008991</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.305674435113917</v>
+        <v>2.277209318631029</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1596832169926042</v>
+        <v>0.1594905162468467</v>
       </c>
       <c r="C83">
-        <v>404.9630146612552</v>
+        <v>398.5701934308194</v>
       </c>
       <c r="D83">
-        <v>912.2220146612553</v>
+        <v>913.7681934308195</v>
       </c>
       <c r="E83">
-        <v>216.659</v>
+        <v>224.5980000000001</v>
       </c>
       <c r="F83">
-        <v>643.0590000000001</v>
+        <v>650.9980000000002</v>
       </c>
       <c r="G83">
         <v>135.8</v>
@@ -8093,28 +8093,28 @@
         <v>111</v>
       </c>
       <c r="M83">
-        <v>48.74387220000001</v>
+        <v>49.34564840000002</v>
       </c>
       <c r="N83">
-        <v>62.25612779999997</v>
+        <v>61.65435159999997</v>
       </c>
       <c r="O83">
-        <v>14.94147067199999</v>
+        <v>14.79704438399999</v>
       </c>
       <c r="P83">
-        <v>47.31465712799998</v>
+        <v>46.85730721599998</v>
       </c>
       <c r="Q83">
-        <v>159.814657128</v>
+        <v>159.357307216</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5948459841716013</v>
+        <v>0.6236219791491485</v>
       </c>
       <c r="T83">
-        <v>2.697667267008991</v>
+        <v>2.839054440332314</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.277209318631029</v>
+        <v>2.24943847328187</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1594905162468467</v>
+        <v>0.1592978155010892</v>
       </c>
       <c r="C84">
-        <v>398.5701934308194</v>
+        <v>392.1826225182092</v>
       </c>
       <c r="D84">
-        <v>913.7681934308195</v>
+        <v>915.3196225182093</v>
       </c>
       <c r="E84">
-        <v>224.5980000000001</v>
+        <v>232.5370000000001</v>
       </c>
       <c r="F84">
-        <v>650.9980000000002</v>
+        <v>658.9370000000001</v>
       </c>
       <c r="G84">
         <v>135.8</v>
@@ -8175,28 +8175,28 @@
         <v>111</v>
       </c>
       <c r="M84">
-        <v>49.34564840000002</v>
+        <v>49.94742460000001</v>
       </c>
       <c r="N84">
-        <v>61.65435159999997</v>
+        <v>61.05257539999997</v>
       </c>
       <c r="O84">
-        <v>14.79704438399999</v>
+        <v>14.65261809599999</v>
       </c>
       <c r="P84">
-        <v>46.85730721599998</v>
+        <v>46.39995730399998</v>
       </c>
       <c r="Q84">
-        <v>159.357307216</v>
+        <v>158.899957304</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6236219791491485</v>
+        <v>0.6557833853005249</v>
       </c>
       <c r="T84">
-        <v>2.839054440332314</v>
+        <v>2.997075398752498</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.24943847328187</v>
+        <v>2.222336804929077</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1592978155010892</v>
+        <v>0.1591051147553317</v>
       </c>
       <c r="C85">
-        <v>392.1826225182092</v>
+        <v>385.8003287114522</v>
       </c>
       <c r="D85">
-        <v>915.3196225182093</v>
+        <v>916.8763287114523</v>
       </c>
       <c r="E85">
-        <v>232.5370000000001</v>
+        <v>240.4760000000001</v>
       </c>
       <c r="F85">
-        <v>658.9370000000001</v>
+        <v>666.8760000000001</v>
       </c>
       <c r="G85">
         <v>135.8</v>
@@ -8257,28 +8257,28 @@
         <v>111</v>
       </c>
       <c r="M85">
-        <v>49.94742460000001</v>
+        <v>50.54920080000001</v>
       </c>
       <c r="N85">
-        <v>61.05257539999997</v>
+        <v>60.45079919999998</v>
       </c>
       <c r="O85">
-        <v>14.65261809599999</v>
+        <v>14.50819180799999</v>
       </c>
       <c r="P85">
-        <v>46.39995730399998</v>
+        <v>45.94260739199999</v>
       </c>
       <c r="Q85">
-        <v>158.899957304</v>
+        <v>158.442607392</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6557833853005249</v>
+        <v>0.6919649672208235</v>
       </c>
       <c r="T85">
-        <v>2.997075398752498</v>
+        <v>3.174848976975206</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.222336804929077</v>
+        <v>2.195880414394207</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1591051147553317</v>
+        <v>0.1589124140095742</v>
       </c>
       <c r="C86">
-        <v>385.8003287114522</v>
+        <v>379.423338981122</v>
       </c>
       <c r="D86">
-        <v>916.8763287114523</v>
+        <v>918.438338981122</v>
       </c>
       <c r="E86">
-        <v>240.4760000000001</v>
+        <v>248.415</v>
       </c>
       <c r="F86">
-        <v>666.8760000000001</v>
+        <v>674.8150000000001</v>
       </c>
       <c r="G86">
         <v>135.8</v>
@@ -8339,28 +8339,28 @@
         <v>111</v>
       </c>
       <c r="M86">
-        <v>50.54920080000001</v>
+        <v>51.15097700000001</v>
       </c>
       <c r="N86">
-        <v>60.45079919999998</v>
+        <v>59.84902299999997</v>
       </c>
       <c r="O86">
-        <v>14.50819180799999</v>
+        <v>14.36376551999999</v>
       </c>
       <c r="P86">
-        <v>45.94260739199999</v>
+        <v>45.48525747999998</v>
       </c>
       <c r="Q86">
-        <v>158.442607392</v>
+        <v>157.98525748</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.691964967220823</v>
+        <v>0.7329707600638279</v>
       </c>
       <c r="T86">
-        <v>3.174848976975203</v>
+        <v>3.376325698960938</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.195880414394207</v>
+        <v>2.170046527166039</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1589124140095742</v>
+        <v>0.1587197132638167</v>
       </c>
       <c r="C87">
-        <v>379.423338981122</v>
+        <v>373.0516804818968</v>
       </c>
       <c r="D87">
-        <v>918.438338981122</v>
+        <v>920.0056804818969</v>
       </c>
       <c r="E87">
-        <v>248.415</v>
+        <v>256.354</v>
       </c>
       <c r="F87">
-        <v>674.8150000000001</v>
+        <v>682.754</v>
       </c>
       <c r="G87">
         <v>135.8</v>
@@ -8421,28 +8421,28 @@
         <v>111</v>
       </c>
       <c r="M87">
-        <v>51.15097700000001</v>
+        <v>51.75275320000001</v>
       </c>
       <c r="N87">
-        <v>59.84902299999997</v>
+        <v>59.24724679999998</v>
       </c>
       <c r="O87">
-        <v>14.36376551999999</v>
+        <v>14.21933923199999</v>
       </c>
       <c r="P87">
-        <v>45.48525747999998</v>
+        <v>45.02790756799998</v>
       </c>
       <c r="Q87">
-        <v>157.98525748</v>
+        <v>157.527907568</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7329707600638279</v>
+        <v>0.7798345233129761</v>
       </c>
       <c r="T87">
-        <v>3.376325698960938</v>
+        <v>3.606584809801777</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.170046527166039</v>
+        <v>2.144813428012946</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1587197132638167</v>
+        <v>0.1585270125180592</v>
       </c>
       <c r="C88">
-        <v>373.0516804818968</v>
+        <v>366.6853805541319</v>
       </c>
       <c r="D88">
-        <v>920.0056804818969</v>
+        <v>921.578380554132</v>
       </c>
       <c r="E88">
-        <v>256.354</v>
+        <v>264.2930000000001</v>
       </c>
       <c r="F88">
-        <v>682.754</v>
+        <v>690.6930000000001</v>
       </c>
       <c r="G88">
         <v>135.8</v>
@@ -8503,28 +8503,28 @@
         <v>111</v>
       </c>
       <c r="M88">
-        <v>51.75275320000001</v>
+        <v>52.35452940000001</v>
       </c>
       <c r="N88">
-        <v>59.24724679999998</v>
+        <v>58.64547059999997</v>
       </c>
       <c r="O88">
-        <v>14.21933923199999</v>
+        <v>14.07491294399999</v>
       </c>
       <c r="P88">
-        <v>45.02790756799998</v>
+        <v>44.57055765599998</v>
       </c>
       <c r="Q88">
-        <v>157.527907568</v>
+        <v>157.070557656</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7798345233129761</v>
+        <v>0.8339080962927627</v>
       </c>
       <c r="T88">
-        <v>3.606584809801777</v>
+        <v>3.872268399233515</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.144813428012946</v>
+        <v>2.120160400104751</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1585270125180592</v>
+        <v>0.1583343117723016</v>
       </c>
       <c r="C89">
-        <v>366.6853805541319</v>
+        <v>360.3244667254512</v>
       </c>
       <c r="D89">
-        <v>921.578380554132</v>
+        <v>923.1564667254513</v>
       </c>
       <c r="E89">
-        <v>264.2930000000001</v>
+        <v>272.232</v>
       </c>
       <c r="F89">
-        <v>690.6930000000001</v>
+        <v>698.6320000000001</v>
       </c>
       <c r="G89">
         <v>135.8</v>
@@ -8585,28 +8585,28 @@
         <v>111</v>
       </c>
       <c r="M89">
-        <v>52.35452940000001</v>
+        <v>52.95630560000001</v>
       </c>
       <c r="N89">
-        <v>58.64547059999997</v>
+        <v>58.04369439999998</v>
       </c>
       <c r="O89">
-        <v>14.07491294399999</v>
+        <v>13.93048665599999</v>
       </c>
       <c r="P89">
-        <v>44.57055765599998</v>
+        <v>44.11320774399999</v>
       </c>
       <c r="Q89">
-        <v>157.070557656</v>
+        <v>156.613207744</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8339080962927627</v>
+        <v>0.896993931435847</v>
       </c>
       <c r="T89">
-        <v>3.872268399233515</v>
+        <v>4.182232586903876</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.120160400104751</v>
+        <v>2.096067668285379</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1583343117723016</v>
+        <v>0.1581416110265441</v>
       </c>
       <c r="C90">
-        <v>360.3244667254512</v>
+        <v>353.9689667123512</v>
       </c>
       <c r="D90">
-        <v>923.1564667254513</v>
+        <v>924.7399667123514</v>
       </c>
       <c r="E90">
-        <v>272.232</v>
+        <v>280.1710000000001</v>
       </c>
       <c r="F90">
-        <v>698.6320000000001</v>
+        <v>706.5710000000001</v>
       </c>
       <c r="G90">
         <v>135.8</v>
@@ -8667,28 +8667,28 @@
         <v>111</v>
       </c>
       <c r="M90">
-        <v>52.95630560000001</v>
+        <v>53.55808180000002</v>
       </c>
       <c r="N90">
-        <v>58.04369439999998</v>
+        <v>57.44191819999997</v>
       </c>
       <c r="O90">
-        <v>13.93048665599999</v>
+        <v>13.78606036799999</v>
       </c>
       <c r="P90">
-        <v>44.11320774399999</v>
+        <v>43.65585783199997</v>
       </c>
       <c r="Q90">
-        <v>156.613207744</v>
+        <v>156.155857832</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.896993931435847</v>
+        <v>0.9715499184231285</v>
       </c>
       <c r="T90">
-        <v>4.182232586903876</v>
+        <v>4.548553899605211</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.096067668285379</v>
+        <v>2.072516346169813</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1581416110265441</v>
+        <v>0.1579489102807866</v>
       </c>
       <c r="C91">
-        <v>353.9689667123512</v>
+        <v>347.6189084218255</v>
       </c>
       <c r="D91">
-        <v>924.7399667123514</v>
+        <v>926.3289084218255</v>
       </c>
       <c r="E91">
-        <v>280.1710000000001</v>
+        <v>288.1100000000001</v>
       </c>
       <c r="F91">
-        <v>706.5710000000001</v>
+        <v>714.5100000000001</v>
       </c>
       <c r="G91">
         <v>135.8</v>
@@ -8749,28 +8749,28 @@
         <v>111</v>
       </c>
       <c r="M91">
-        <v>53.55808180000002</v>
+        <v>54.15985800000001</v>
       </c>
       <c r="N91">
-        <v>57.44191819999997</v>
+        <v>56.84014199999997</v>
       </c>
       <c r="O91">
-        <v>13.78606036799999</v>
+        <v>13.64163407999999</v>
       </c>
       <c r="P91">
-        <v>43.65585783199997</v>
+        <v>43.19850791999998</v>
       </c>
       <c r="Q91">
-        <v>156.155857832</v>
+        <v>155.69850792</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9715499184231285</v>
+        <v>1.061017102807867</v>
       </c>
       <c r="T91">
-        <v>4.548553899605211</v>
+        <v>4.988139474846814</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.072516346169813</v>
+        <v>2.049488386767926</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1579489102807866</v>
+        <v>0.1577562095350291</v>
       </c>
       <c r="C92">
-        <v>347.6189084218255</v>
+        <v>341.2743199530037</v>
       </c>
       <c r="D92">
-        <v>926.3289084218255</v>
+        <v>927.9233199530037</v>
       </c>
       <c r="E92">
-        <v>288.1100000000001</v>
+        <v>296.049</v>
       </c>
       <c r="F92">
-        <v>714.5100000000001</v>
+        <v>722.4490000000001</v>
       </c>
       <c r="G92">
         <v>135.8</v>
@@ -8831,28 +8831,28 @@
         <v>111</v>
       </c>
       <c r="M92">
-        <v>54.15985800000001</v>
+        <v>54.76163420000001</v>
       </c>
       <c r="N92">
-        <v>56.84014199999997</v>
+        <v>56.23836579999998</v>
       </c>
       <c r="O92">
-        <v>13.64163407999999</v>
+        <v>13.49720779199999</v>
       </c>
       <c r="P92">
-        <v>43.19850791999998</v>
+        <v>42.74115800799999</v>
       </c>
       <c r="Q92">
-        <v>155.69850792</v>
+        <v>155.241158008</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.061017102807867</v>
+        <v>1.170365883722546</v>
       </c>
       <c r="T92">
-        <v>4.988139474846814</v>
+        <v>5.525410733475439</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.049488386767926</v>
+        <v>2.026966536363883</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1577562095350291</v>
+        <v>0.1575635087892716</v>
       </c>
       <c r="C93">
-        <v>341.2743199530037</v>
+        <v>334.935229598806</v>
       </c>
       <c r="D93">
-        <v>927.9233199530037</v>
+        <v>929.5232295988062</v>
       </c>
       <c r="E93">
-        <v>296.049</v>
+        <v>303.9880000000001</v>
       </c>
       <c r="F93">
-        <v>722.4490000000001</v>
+        <v>730.3880000000001</v>
       </c>
       <c r="G93">
         <v>135.8</v>
@@ -8913,28 +8913,28 @@
         <v>111</v>
       </c>
       <c r="M93">
-        <v>54.76163420000001</v>
+        <v>55.36341040000001</v>
       </c>
       <c r="N93">
-        <v>56.23836579999998</v>
+        <v>55.63658959999997</v>
       </c>
       <c r="O93">
-        <v>13.49720779199999</v>
+        <v>13.35278150399999</v>
       </c>
       <c r="P93">
-        <v>42.74115800799999</v>
+        <v>42.28380809599998</v>
       </c>
       <c r="Q93">
-        <v>155.241158008</v>
+        <v>154.783808096</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.170365883722546</v>
+        <v>1.307051859865896</v>
       </c>
       <c r="T93">
-        <v>5.525410733475439</v>
+        <v>6.196999806761223</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.026966536363883</v>
+        <v>2.004934291403406</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1575635087892716</v>
+        <v>0.1674073680435141</v>
       </c>
       <c r="C94">
-        <v>334.935229598806</v>
+        <v>251.7532900226003</v>
       </c>
       <c r="D94">
-        <v>929.5232295988062</v>
+        <v>854.2802900226003</v>
       </c>
       <c r="E94">
-        <v>303.9880000000001</v>
+        <v>311.9270000000001</v>
       </c>
       <c r="F94">
-        <v>730.3880000000001</v>
+        <v>738.3270000000001</v>
       </c>
       <c r="G94">
         <v>135.8</v>
@@ -8995,45 +8995,45 @@
         <v>111</v>
       </c>
       <c r="M94">
-        <v>55.36341040000001</v>
+        <v>66.44943000000001</v>
       </c>
       <c r="N94">
-        <v>55.63658959999997</v>
+        <v>44.55056999999998</v>
       </c>
       <c r="O94">
-        <v>13.35278150399999</v>
+        <v>10.69213679999999</v>
       </c>
       <c r="P94">
-        <v>42.28380809599998</v>
+        <v>33.85843319999999</v>
       </c>
       <c r="Q94">
-        <v>154.783808096</v>
+        <v>146.3584332</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.307051859865896</v>
+        <v>1.482790972050203</v>
       </c>
       <c r="T94">
-        <v>6.196999806761223</v>
+        <v>7.060471472414371</v>
       </c>
       <c r="U94">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V94">
         <v>0.24</v>
       </c>
       <c r="W94">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y94">
-        <v>2.004934291403406</v>
+        <v>1.670443222763536</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1674073680435141</v>
+        <v>0.1673225872977566</v>
       </c>
       <c r="C95">
-        <v>251.7532900226003</v>
+        <v>244.4102822713219</v>
       </c>
       <c r="D95">
-        <v>854.2802900226003</v>
+        <v>854.876282271322</v>
       </c>
       <c r="E95">
-        <v>311.9270000000001</v>
+        <v>319.866</v>
       </c>
       <c r="F95">
-        <v>738.3270000000001</v>
+        <v>746.2660000000001</v>
       </c>
       <c r="G95">
         <v>135.8</v>
@@ -9077,28 +9077,28 @@
         <v>111</v>
       </c>
       <c r="M95">
-        <v>66.44943000000001</v>
+        <v>67.16394000000001</v>
       </c>
       <c r="N95">
-        <v>44.55056999999998</v>
+        <v>43.83605999999997</v>
       </c>
       <c r="O95">
-        <v>10.69213679999999</v>
+        <v>10.52065439999999</v>
       </c>
       <c r="P95">
-        <v>33.85843319999999</v>
+        <v>33.31540559999998</v>
       </c>
       <c r="Q95">
-        <v>146.3584332</v>
+        <v>145.8154056</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.482790972050203</v>
+        <v>1.717109788295945</v>
       </c>
       <c r="T95">
-        <v>7.060471472414371</v>
+        <v>8.21176702661857</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.670443222763536</v>
+        <v>1.652672550180945</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1673225872977566</v>
+        <v>0.1672378065519991</v>
       </c>
       <c r="C96">
-        <v>244.4102822713219</v>
+        <v>237.0681066936268</v>
       </c>
       <c r="D96">
-        <v>854.876282271322</v>
+        <v>855.4731066936268</v>
       </c>
       <c r="E96">
-        <v>319.866</v>
+        <v>327.8050000000001</v>
       </c>
       <c r="F96">
-        <v>746.2660000000001</v>
+        <v>754.2050000000002</v>
       </c>
       <c r="G96">
         <v>135.8</v>
@@ -9159,28 +9159,28 @@
         <v>111</v>
       </c>
       <c r="M96">
-        <v>67.16394000000001</v>
+        <v>67.87845000000002</v>
       </c>
       <c r="N96">
-        <v>43.83605999999997</v>
+        <v>43.12154999999997</v>
       </c>
       <c r="O96">
-        <v>10.52065439999999</v>
+        <v>10.34917199999999</v>
       </c>
       <c r="P96">
-        <v>33.31540559999998</v>
+        <v>32.77237799999997</v>
       </c>
       <c r="Q96">
-        <v>145.8154056</v>
+        <v>145.272378</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.717109788295945</v>
+        <v>2.045156131039985</v>
       </c>
       <c r="T96">
-        <v>8.21176702661857</v>
+        <v>9.823580802504452</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.652672550180945</v>
+        <v>1.635275997021145</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1672378065519991</v>
+        <v>0.1671530258062416</v>
       </c>
       <c r="C97">
-        <v>237.0681066936268</v>
+        <v>229.7267650336568</v>
       </c>
       <c r="D97">
-        <v>855.4731066936268</v>
+        <v>856.0707650336569</v>
       </c>
       <c r="E97">
-        <v>327.8050000000001</v>
+        <v>335.7440000000001</v>
       </c>
       <c r="F97">
-        <v>754.2050000000002</v>
+        <v>762.1440000000001</v>
       </c>
       <c r="G97">
         <v>135.8</v>
@@ -9241,28 +9241,28 @@
         <v>111</v>
       </c>
       <c r="M97">
-        <v>67.87845000000002</v>
+        <v>68.59296000000001</v>
       </c>
       <c r="N97">
-        <v>43.12154999999997</v>
+        <v>42.40703999999998</v>
       </c>
       <c r="O97">
-        <v>10.34917199999999</v>
+        <v>10.1776896</v>
       </c>
       <c r="P97">
-        <v>32.77237799999997</v>
+        <v>32.22935039999999</v>
       </c>
       <c r="Q97">
-        <v>145.272378</v>
+        <v>144.7293504</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.045156131039985</v>
+        <v>2.537225645156044</v>
       </c>
       <c r="T97">
-        <v>9.823580802504452</v>
+        <v>12.24130146633327</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.635275997021145</v>
+        <v>1.618241872052175</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1671530258062416</v>
+        <v>0.1670682450604841</v>
       </c>
       <c r="C98">
-        <v>229.7267650336569</v>
+        <v>222.3862590404312</v>
       </c>
       <c r="D98">
-        <v>856.0707650336569</v>
+        <v>856.6692590404314</v>
       </c>
       <c r="E98">
-        <v>335.744</v>
+        <v>343.683</v>
       </c>
       <c r="F98">
-        <v>762.144</v>
+        <v>770.0830000000001</v>
       </c>
       <c r="G98">
         <v>135.8</v>
@@ -9323,28 +9323,28 @@
         <v>111</v>
       </c>
       <c r="M98">
-        <v>68.59296000000001</v>
+        <v>69.30747000000001</v>
       </c>
       <c r="N98">
-        <v>42.40703999999998</v>
+        <v>41.69252999999998</v>
       </c>
       <c r="O98">
-        <v>10.1776896</v>
+        <v>10.00620719999999</v>
       </c>
       <c r="P98">
-        <v>32.22935039999999</v>
+        <v>31.68632279999999</v>
       </c>
       <c r="Q98">
-        <v>144.7293504</v>
+        <v>144.1863228</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.537225645156037</v>
+        <v>3.357341502016133</v>
       </c>
       <c r="T98">
-        <v>12.24130146633324</v>
+        <v>16.27083590604792</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.618241872052175</v>
+        <v>1.60155896615473</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1670682450604841</v>
+        <v>0.1669834643147265</v>
       </c>
       <c r="C99">
-        <v>222.3862590404312</v>
+        <v>215.0465904678641</v>
       </c>
       <c r="D99">
-        <v>856.6692590404314</v>
+        <v>857.2685904678641</v>
       </c>
       <c r="E99">
-        <v>343.683</v>
+        <v>351.622</v>
       </c>
       <c r="F99">
-        <v>770.0830000000001</v>
+        <v>778.022</v>
       </c>
       <c r="G99">
         <v>135.8</v>
@@ -9405,28 +9405,28 @@
         <v>111</v>
       </c>
       <c r="M99">
-        <v>69.30747000000001</v>
+        <v>70.02198</v>
       </c>
       <c r="N99">
-        <v>41.69252999999998</v>
+        <v>40.97801999999999</v>
       </c>
       <c r="O99">
-        <v>10.00620719999999</v>
+        <v>9.834724799999996</v>
       </c>
       <c r="P99">
-        <v>31.68632279999999</v>
+        <v>31.14329519999999</v>
       </c>
       <c r="Q99">
-        <v>144.1863228</v>
+        <v>143.6432952</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.357341502016133</v>
+        <v>4.997573215736323</v>
       </c>
       <c r="T99">
-        <v>16.27083590604792</v>
+        <v>24.32990478547729</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.60155896615473</v>
+        <v>1.58521652772458</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1669834643147265</v>
+        <v>0.166898683568969</v>
       </c>
       <c r="C100">
-        <v>215.0465904678641</v>
+        <v>207.7077610747803</v>
       </c>
       <c r="D100">
-        <v>857.2685904678641</v>
+        <v>857.8687610747804</v>
       </c>
       <c r="E100">
-        <v>351.622</v>
+        <v>359.5610000000001</v>
       </c>
       <c r="F100">
-        <v>778.022</v>
+        <v>785.9610000000001</v>
       </c>
       <c r="G100">
         <v>135.8</v>
@@ -9487,28 +9487,28 @@
         <v>111</v>
       </c>
       <c r="M100">
-        <v>70.02198</v>
+        <v>70.73649</v>
       </c>
       <c r="N100">
-        <v>40.97801999999999</v>
+        <v>40.26350999999998</v>
       </c>
       <c r="O100">
-        <v>9.834724799999996</v>
+        <v>9.663242399999996</v>
       </c>
       <c r="P100">
-        <v>31.14329519999999</v>
+        <v>30.60026759999999</v>
       </c>
       <c r="Q100">
-        <v>143.6432952</v>
+        <v>143.1002676</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.997573215736323</v>
+        <v>9.918268356896895</v>
       </c>
       <c r="T100">
-        <v>24.32990478547729</v>
+        <v>48.50711142376539</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.58521652772458</v>
+        <v>1.569204239565746</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.166898683568969</v>
-      </c>
-      <c r="C101">
-        <v>207.7077610747803</v>
-      </c>
-      <c r="D101">
-        <v>857.8687610747804</v>
-      </c>
-      <c r="E101">
-        <v>359.5610000000001</v>
-      </c>
-      <c r="F101">
-        <v>785.9610000000001</v>
-      </c>
-      <c r="G101">
-        <v>135.8</v>
-      </c>
-      <c r="H101">
-        <v>367.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>223.5</v>
-      </c>
-      <c r="K101">
-        <v>112.5</v>
-      </c>
-      <c r="L101">
-        <v>111</v>
-      </c>
-      <c r="M101">
-        <v>70.73649</v>
-      </c>
-      <c r="N101">
-        <v>40.26350999999998</v>
-      </c>
-      <c r="O101">
-        <v>9.663242399999996</v>
-      </c>
-      <c r="P101">
-        <v>30.60026759999999</v>
-      </c>
-      <c r="Q101">
-        <v>143.1002676</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.918268356896895</v>
-      </c>
-      <c r="T101">
-        <v>48.50711142376539</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.24</v>
-      </c>
-      <c r="W101">
-        <v>0.0684</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.569204239565746</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
